--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 1855-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44884</v>
+        <v>45671</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -647,12 +647,130 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Gammelgransskål
+Tretåig hackspett
+Ullticka
+Lappranunkel
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Z2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 41136-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
         <v>26</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>26</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -662,157 +780,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 1855-2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Gammelgransskål
-Tretåig hackspett
-Ullticka
-Lappranunkel
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 63800-2023</t>
+          <t>A 21714-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45278</v>
+        <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1099,159 +1099,159 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 63800-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Trana</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 21714-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49284-2022</t>
+          <t>A 28542-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44861</v>
+        <v>44748</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28542-2022</t>
+          <t>A 49284-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44748</v>
+        <v>44861</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 52000-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45716</v>
+        <v>44463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45173</v>
+        <v>45359</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45173</v>
+        <v>44579</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45405</v>
+        <v>45685</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44901</v>
+        <v>45099</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45103</v>
+        <v>45261</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44872</v>
+        <v>45716</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45636</v>
+        <v>45076</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45590</v>
+        <v>45645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45824</v>
+        <v>46007</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>17.8</v>
+        <v>4.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45581</v>
+        <v>46006</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45835</v>
+        <v>46007</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>10.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45359</v>
+        <v>45796</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>10.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45894</v>
+        <v>46007</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45180</v>
+        <v>45209</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45903</v>
+        <v>45579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45903</v>
+        <v>46008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45910</v>
+        <v>46008</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46073</v>
+        <v>45068</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45922</v>
+        <v>46009</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45922</v>
+        <v>45894</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45922</v>
+        <v>45636</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>18.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45581</v>
+        <v>45636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44482</v>
+        <v>45597</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45645</v>
+        <v>45824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10.5</v>
+        <v>17.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45936</v>
+        <v>45903</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44750</v>
+        <v>45903</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4346,13 +4346,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4395,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4409,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45943</v>
+        <v>44629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4425,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>13.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4468,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4482,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45945</v>
+        <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4498,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4541,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4555,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45946</v>
+        <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4571,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4614,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4628,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45946</v>
+        <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4644,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4687,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4701,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45953</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4717,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4760,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4774,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45953</v>
+        <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4790,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4833,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4847,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45217</v>
+        <v>45639</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4863,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.9</v>
+        <v>10.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4906,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4920,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45685</v>
+        <v>45581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4936,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4979,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4993,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45685</v>
+        <v>45936</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5009,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11.1</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5052,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5066,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45968</v>
+        <v>46073</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5082,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5125,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5139,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45966</v>
+        <v>45597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5155,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5198,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5212,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45197</v>
+        <v>45943</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5228,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5271,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5285,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45973</v>
+        <v>45945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5301,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5344,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5358,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45973</v>
+        <v>45946</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5374,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.9</v>
+        <v>8.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5417,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5431,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44629</v>
+        <v>45946</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5447,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>13.3</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5490,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5504,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45044</v>
+        <v>44872</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5520,7 +5515,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5563,7 +5558,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5577,10 +5572,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45986</v>
+        <v>45597</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5593,7 +5588,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5636,7 +5631,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5646,14 +5641,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46126</v>
+        <v>45953</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5666,7 +5661,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5709,7 +5704,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5723,10 +5718,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45987</v>
+        <v>45369</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5739,7 +5734,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.9</v>
+        <v>12.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5782,7 +5777,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19135-2026</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5796,10 +5791,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46132</v>
+        <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5807,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5850,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45987</v>
+        <v>45520</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5880,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5923,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5942,10 +5937,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45989</v>
+        <v>45966</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5953,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +5996,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50257-2021</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44458</v>
+        <v>45103</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6026,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6069,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6088,10 +6083,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44813</v>
+        <v>45645</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6104,7 +6099,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6147,7 +6142,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6157,14 +6152,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46002</v>
+        <v>46126</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6177,7 +6172,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6215,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6229,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46002</v>
+        <v>45968</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6245,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6288,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6302,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45597</v>
+        <v>45044</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6318,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6361,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6375,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46002</v>
+        <v>45197</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6391,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6434,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 19135-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6448,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46002</v>
+        <v>46132</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6464,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6507,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6521,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46006</v>
+        <v>45973</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6537,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6580,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6599,10 +6594,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45278</v>
+        <v>45973</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6610,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6653,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6667,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46007</v>
+        <v>45716</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6683,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6726,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6740,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46007</v>
+        <v>45987</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6756,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6799,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6813,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46007</v>
+        <v>45987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6829,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>10.2</v>
+        <v>4.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6872,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6886,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46008</v>
+        <v>45986</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6902,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6945,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6964,10 +6959,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46008</v>
+        <v>45989</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6975,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7018,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7033,14 +7028,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46009</v>
+        <v>45142</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7048,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.1</v>
+        <v>4.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7091,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7106,14 +7101,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45303</v>
+        <v>45581</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7121,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7164,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7179,14 +7174,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45369</v>
+        <v>45610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7194,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>12.4</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7237,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7256,10 +7251,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7267,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7310,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7329,10 +7324,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44949</v>
+        <v>46002</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7340,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7383,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7397,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44508</v>
+        <v>46002</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7413,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7456,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7471,14 +7466,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45142</v>
+        <v>46002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7491,7 +7486,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7534,7 +7529,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7548,10 +7543,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45671</v>
+        <v>45873</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7564,7 +7559,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7602,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7621,10 +7616,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45873</v>
+        <v>45636</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7632,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7675,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7689,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45603</v>
+        <v>46009</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7705,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.8</v>
+        <v>8.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7748,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7763,14 +7758,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44908</v>
+        <v>45078</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7778,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7821,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7840,10 +7835,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44957</v>
+        <v>46146</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7851,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7894,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7908,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45639</v>
+        <v>45229</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7924,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>10.3</v>
+        <v>5.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7967,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7981,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45597</v>
+        <v>46146</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +7997,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8040,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8059,10 +8054,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45415</v>
+        <v>45425</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8074,8 +8069,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>13.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45129</v>
+        <v>45181</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45355</v>
+        <v>45671</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>27.1</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46146</v>
+        <v>46155</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45636</v>
+        <v>45279</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>18.6</v>
+        <v>3.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44579</v>
+        <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45636</v>
+        <v>45462</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45103</v>
+        <v>46009</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46154</v>
+        <v>45974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45078</v>
+        <v>45974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>15.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8848,7 +8848,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45974</v>
+        <v>45405</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8921,7 +8921,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46155</v>
+        <v>45405</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44586</v>
+        <v>45642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.9</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9067,7 +9067,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9081,10 +9081,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45716</v>
+        <v>44957</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9140,7 +9140,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45974</v>
+        <v>45208</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9213,7 +9213,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46009</v>
+        <v>46200</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9286,7 +9286,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9300,10 +9300,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45462</v>
+        <v>46247</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>11.1</v>
+        <v>2.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9373,10 +9373,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45974</v>
+        <v>46206</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>15.3</v>
+        <v>2.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9432,7 +9432,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9442,14 +9442,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45645</v>
+        <v>44908</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9505,7 +9505,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45181</v>
+        <v>45716</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9578,7 +9578,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45229</v>
+        <v>45716</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9651,7 +9651,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9665,10 +9665,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45642</v>
+        <v>44813</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>11.7</v>
+        <v>4.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9724,7 +9724,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45642</v>
+        <v>46253</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9797,7 +9797,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45191</v>
+        <v>46258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>14.9</v>
+        <v>3.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9870,7 +9870,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9884,10 +9884,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45208</v>
+        <v>45642</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.3</v>
+        <v>11.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9943,7 +9943,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9957,10 +9957,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44817</v>
+        <v>45642</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10016,7 +10016,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10030,10 +10030,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45279</v>
+        <v>44750</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10045,8 +10045,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10089,7 +10094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10103,10 +10108,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45716</v>
+        <v>45603</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10119,7 +10124,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10162,7 +10167,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10176,10 +10181,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45716</v>
+        <v>45278</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10235,7 +10240,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10249,10 +10254,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45671</v>
+        <v>46272</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10265,7 +10270,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10308,7 +10313,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10322,10 +10327,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44907</v>
+        <v>46272</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10338,7 +10343,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10381,7 +10386,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10395,10 +10400,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45261</v>
+        <v>46269</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10411,7 +10416,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10454,7 +10459,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10468,10 +10473,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45520</v>
+        <v>44508</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10484,7 +10489,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10527,7 +10532,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10541,10 +10546,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46200</v>
+        <v>44482</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10557,7 +10562,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10600,7 +10605,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10614,10 +10619,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46247</v>
+        <v>46275</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10630,7 +10635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10673,7 +10678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10687,10 +10692,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44902</v>
+        <v>45671</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10703,7 +10708,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10746,7 +10751,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10760,10 +10765,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45597</v>
+        <v>44817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10776,7 +10781,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10819,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 52000-2021</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10833,10 +10838,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44463</v>
+        <v>45256</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10849,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10892,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10906,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46206</v>
+        <v>45173</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10922,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10965,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10979,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45076</v>
+        <v>45173</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -10995,7 +11000,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>10.5</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11038,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11052,10 +11057,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45103</v>
+        <v>45405</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11068,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11111,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11125,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45256</v>
+        <v>44901</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11141,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>12.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11184,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11198,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46253</v>
+        <v>45415</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11214,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11257,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11271,10 +11276,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46258</v>
+        <v>45191</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11287,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.1</v>
+        <v>14.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11330,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 50257-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11344,10 +11349,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45642</v>
+        <v>44458</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11360,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11403,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11417,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45425</v>
+        <v>45217</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11432,13 +11437,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>13.9</v>
+        <v>4.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45553</v>
+        <v>45129</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>11.7</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45700</v>
+        <v>45590</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45405</v>
+        <v>44586</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45405</v>
+        <v>44949</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45229</v>
+        <v>45103</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45099</v>
+        <v>45229</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45610</v>
+        <v>45303</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44928</v>
+        <v>45180</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46272</v>
+        <v>45355</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>27.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46272</v>
+        <v>45103</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46269</v>
+        <v>45700</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46275</v>
+        <v>45685</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.8</v>
+        <v>11.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45776</v>
+        <v>44902</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.4</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44889</v>
+        <v>45553</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>7.3</v>
+        <v>11.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45789</v>
+        <v>44907</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45789</v>
+        <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45796</v>
+        <v>44889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>10.9</v>
+        <v>7.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45209</v>
+        <v>45776</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.2</v>
+        <v>8.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45579</v>
+        <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45068</v>
+        <v>45789</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 1855-2025</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45671</v>
+        <v>44884</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -647,12 +647,122 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
+        <v>26</v>
+      </c>
+      <c r="U2" t="n">
+        <v>26</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gammelgransskål
+Vedskivlav
+Nästlav
+Vedticka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 1855-2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45671</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gammelgransskål
@@ -662,115 +772,115 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 41136-2023</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>45173</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E4" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>5.7</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S4" t="n">
         <v>6</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>26</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>26</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -780,145 +890,35 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 54858-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44884</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>26</v>
-      </c>
-      <c r="U4" t="n">
-        <v>26</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gammelgransskål
-Vedskivlav
-Nästlav
-Vedticka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28542-2022</t>
+          <t>A 49284-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44748</v>
+        <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49284-2022</t>
+          <t>A 28542-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44861</v>
+        <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54997-2022</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44886</v>
+        <v>45716</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54632-2022</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44883</v>
+        <v>45173</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30003-2022</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44756</v>
+        <v>45173</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47661-2022</t>
+          <t>A 54997-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44854</v>
+        <v>44886</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>9.9</v>
+        <v>6.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60754-2021</t>
+          <t>A 54632-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44496</v>
+        <v>44883</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 71446-2021</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44540</v>
+        <v>45405</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52000-2021</t>
+          <t>A 30003-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44463</v>
+        <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45359</v>
+        <v>45642</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>11.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44579</v>
+        <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 47661-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45685</v>
+        <v>44854</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>9.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45099</v>
+        <v>45191</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>14.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45261</v>
+        <v>45208</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 71446-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45716</v>
+        <v>44540</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 60754-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45076</v>
+        <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.5</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45645</v>
+        <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>12.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46007</v>
+        <v>45103</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46006</v>
+        <v>44817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46007</v>
+        <v>45279</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10.2</v>
+        <v>3.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45796</v>
+        <v>45894</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46007</v>
+        <v>45716</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45209</v>
+        <v>45716</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45579</v>
+        <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46008</v>
+        <v>45903</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46008</v>
+        <v>45903</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45068</v>
+        <v>45636</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46009</v>
+        <v>45590</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45894</v>
+        <v>45910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45636</v>
+        <v>45922</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>18.6</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45636</v>
+        <v>45922</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45597</v>
+        <v>45922</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4181,14 +4181,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45824</v>
+        <v>46126</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>17.8</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45903</v>
+        <v>45671</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 19135-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45903</v>
+        <v>46132</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44629</v>
+        <v>44907</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>13.3</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45910</v>
+        <v>45936</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45835</v>
+        <v>45261</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45922</v>
+        <v>45520</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>45581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45922</v>
+        <v>45359</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45639</v>
+        <v>45943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10.3</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45581</v>
+        <v>45945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45936</v>
+        <v>45946</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46073</v>
+        <v>45946</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45597</v>
+        <v>46009</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45943</v>
+        <v>45953</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45945</v>
+        <v>45953</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45946</v>
+        <v>45180</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.5</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45946</v>
+        <v>45873</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44872</v>
+        <v>45968</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5558,7 +5558,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45597</v>
+        <v>45966</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45953</v>
+        <v>45581</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5704,7 +5704,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45369</v>
+        <v>45973</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>12.4</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5777,7 +5777,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45953</v>
+        <v>45973</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45520</v>
+        <v>44482</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45966</v>
+        <v>45645</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>10.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5996,7 +5996,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45103</v>
+        <v>45986</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6069,7 +6069,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45645</v>
+        <v>45987</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6152,14 +6152,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46126</v>
+        <v>45987</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6215,7 +6215,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45968</v>
+        <v>44750</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6244,8 +6244,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6288,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6302,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45044</v>
+        <v>45989</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6318,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6361,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6375,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45197</v>
+        <v>46146</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6391,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6434,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19135-2026</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6448,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6464,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6507,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6521,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45973</v>
+        <v>46002</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6537,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6580,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6594,10 +6599,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45973</v>
+        <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6610,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45716</v>
+        <v>44902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6683,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6740,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45987</v>
+        <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6756,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6799,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6813,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45987</v>
+        <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6829,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6872,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6886,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45986</v>
+        <v>46006</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6902,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6945,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6959,10 +6964,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45989</v>
+        <v>46154</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6975,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7018,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7028,14 +7033,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45142</v>
+        <v>45217</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7048,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7091,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7105,10 +7110,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45581</v>
+        <v>46007</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7121,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7164,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7174,14 +7179,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45610</v>
+        <v>46007</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7194,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7237,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7251,10 +7256,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7267,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>10.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7310,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7324,10 +7329,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7340,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7383,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7397,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46002</v>
+        <v>45685</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7413,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7456,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7470,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46002</v>
+        <v>45685</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7486,7 +7491,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9</v>
+        <v>11.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7529,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7543,10 +7548,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45873</v>
+        <v>46008</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7559,7 +7564,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.9</v>
+        <v>0.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7602,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7616,10 +7621,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45636</v>
+        <v>45974</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7632,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7675,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7689,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46009</v>
+        <v>45597</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7705,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>8.1</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7748,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7762,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45078</v>
+        <v>46155</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7778,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7821,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7835,10 +7840,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46146</v>
+        <v>45197</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7851,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7894,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7908,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45229</v>
+        <v>46009</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7924,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.7</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7967,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7981,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46146</v>
+        <v>44629</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7997,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>13.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8040,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8054,10 +8059,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45425</v>
+        <v>45044</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8069,13 +8074,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>13.9</v>
+        <v>5.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45181</v>
+        <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 52000-2021</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45671</v>
+        <v>44463</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46155</v>
+        <v>46009</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46154</v>
+        <v>45462</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.8</v>
+        <v>11.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45279</v>
+        <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.2</v>
+        <v>15.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 50257-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>44458</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45462</v>
+        <v>44813</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>11.1</v>
+        <v>4.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46009</v>
+        <v>45076</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45974</v>
+        <v>45597</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45974</v>
+        <v>45278</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>15.3</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8848,7 +8848,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45405</v>
+        <v>45639</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>10.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8921,7 +8921,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45405</v>
+        <v>45103</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9004,14 +9004,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45642</v>
+        <v>45303</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9067,7 +9067,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9081,10 +9081,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44957</v>
+        <v>45369</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>12.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9140,7 +9140,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45208</v>
+        <v>44949</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9213,7 +9213,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46200</v>
+        <v>44508</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9286,7 +9286,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9300,10 +9300,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46247</v>
+        <v>45256</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9369,14 +9369,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46206</v>
+        <v>45142</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9432,7 +9432,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9442,14 +9442,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44908</v>
+        <v>45671</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9505,7 +9505,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45716</v>
+        <v>46073</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9578,7 +9578,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45716</v>
+        <v>45603</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9651,7 +9651,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9661,14 +9661,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44813</v>
+        <v>44908</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9724,7 +9724,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46253</v>
+        <v>44957</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9797,7 +9797,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46258</v>
+        <v>45642</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9870,7 +9870,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9884,10 +9884,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45642</v>
+        <v>45425</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9899,8 +9899,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>11.7</v>
+        <v>13.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9943,7 +9948,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9957,10 +9962,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45642</v>
+        <v>45553</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9973,7 +9978,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>11.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10016,7 +10021,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10030,10 +10035,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44750</v>
+        <v>45597</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10045,13 +10050,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10094,7 +10094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10108,10 +10108,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45603</v>
+        <v>45700</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10167,7 +10167,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45278</v>
+        <v>46200</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10240,7 +10240,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46272</v>
+        <v>45405</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10313,7 +10313,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10327,10 +10327,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46272</v>
+        <v>45405</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10386,7 +10386,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46269</v>
+        <v>45415</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10459,7 +10459,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10473,10 +10473,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44508</v>
+        <v>45229</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10532,7 +10532,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44482</v>
+        <v>45129</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10605,7 +10605,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46275</v>
+        <v>46247</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10678,7 +10678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10692,10 +10692,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45671</v>
+        <v>45355</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>27.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44817</v>
+        <v>45636</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.9</v>
+        <v>18.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10838,10 +10838,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45256</v>
+        <v>44579</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10897,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45173</v>
+        <v>46206</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45173</v>
+        <v>45636</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11057,10 +11057,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45405</v>
+        <v>45103</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11116,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44901</v>
+        <v>45099</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45415</v>
+        <v>45078</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45191</v>
+        <v>46253</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>14.9</v>
+        <v>6.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 50257-2021</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11345,14 +11345,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44458</v>
+        <v>45610</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45217</v>
+        <v>46258</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45129</v>
+        <v>44586</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45590</v>
+        <v>45716</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44586</v>
+        <v>44928</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>7.9</v>
+        <v>3.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44949</v>
+        <v>45645</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45103</v>
+        <v>45181</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11863,7 +11863,7 @@
         <v>45229</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11929,14 +11929,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45303</v>
+        <v>46272</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45180</v>
+        <v>46272</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45355</v>
+        <v>46269</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>27.1</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45103</v>
+        <v>46275</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45700</v>
+        <v>45776</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45685</v>
+        <v>44889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44902</v>
+        <v>45789</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45553</v>
+        <v>45789</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>11.7</v>
+        <v>5.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44907</v>
+        <v>45796</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>10.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44928</v>
+        <v>45209</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44889</v>
+        <v>45579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45776</v>
+        <v>45068</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45789</v>
+        <v>45824</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.5</v>
+        <v>17.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45789</v>
+        <v>45835</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 1855-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44884</v>
+        <v>45671</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -647,12 +647,130 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Gammelgransskål
+Tretåig hackspett
+Ullticka
+Lappranunkel
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Z2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 41136-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
         <v>26</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>26</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -662,157 +780,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 1855-2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Gammelgransskål
-Tretåig hackspett
-Ullticka
-Lappranunkel
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 21714-2026</t>
+          <t>A 63800-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46149</v>
+        <v>45278</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1099,155 +1099,155 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 21714-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Rödvingetrast</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 63800-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45278</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Trana</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 54997-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45716</v>
+        <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 54632-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45173</v>
+        <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 30003-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45173</v>
+        <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54997-2022</t>
+          <t>A 47661-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44886</v>
+        <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.3</v>
+        <v>9.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54632-2022</t>
+          <t>A 60754-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44883</v>
+        <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 71446-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45405</v>
+        <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30003-2022</t>
+          <t>A 52000-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44756</v>
+        <v>44463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45642</v>
+        <v>44579</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>11.7</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45642</v>
+        <v>45685</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47661-2022</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44854</v>
+        <v>45099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>9.9</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45191</v>
+        <v>45716</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>14.9</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45208</v>
+        <v>45261</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 71446-2021</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44540</v>
+        <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60754-2021</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44496</v>
+        <v>45076</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>10.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44901</v>
+        <v>45645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45103</v>
+        <v>45209</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44817</v>
+        <v>45579</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45279</v>
+        <v>45636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>18.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45894</v>
+        <v>45636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45716</v>
+        <v>45597</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45716</v>
+        <v>45068</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>8.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44872</v>
+        <v>44629</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>13.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45903</v>
+        <v>45894</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45903</v>
+        <v>45824</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>17.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45636</v>
+        <v>45903</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45590</v>
+        <v>45903</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45910</v>
+        <v>45835</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45922</v>
+        <v>45910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45922</v>
+        <v>45581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45922</v>
+        <v>45597</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4181,14 +4181,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46126</v>
+        <v>45922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45671</v>
+        <v>45922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19135-2026</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46132</v>
+        <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44907</v>
+        <v>44872</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45936</v>
+        <v>45597</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45261</v>
+        <v>45369</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>9.199999999999999</v>
+        <v>12.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45520</v>
+        <v>45936</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45581</v>
+        <v>45943</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45359</v>
+        <v>45945</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45943</v>
+        <v>45946</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.7</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45946</v>
+        <v>45953</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.5</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45946</v>
+        <v>45953</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46009</v>
+        <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45953</v>
+        <v>45639</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>10.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45953</v>
+        <v>45103</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45180</v>
+        <v>45645</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45873</v>
+        <v>45044</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45968</v>
+        <v>45197</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5575,7 +5575,7 @@
         <v>45966</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45581</v>
+        <v>45968</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5721,7 +5721,7 @@
         <v>45973</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45973</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44482</v>
+        <v>45716</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45645</v>
+        <v>46073</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5996,7 +5996,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6069,7 +6069,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6079,14 +6079,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45987</v>
+        <v>45142</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6159,7 +6159,7 @@
         <v>45987</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6215,7 +6215,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44750</v>
+        <v>45986</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6244,13 +6244,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6310,7 +6305,7 @@
         <v>45989</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6366,7 +6361,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6375,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46146</v>
+        <v>45581</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6391,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6434,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6449,14 +6444,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46146</v>
+        <v>45610</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6464,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6529,7 +6524,7 @@
         <v>46002</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6585,7 +6580,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6602,7 +6597,7 @@
         <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6610,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6653,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6667,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44902</v>
+        <v>46002</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6683,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6726,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6748,7 +6743,7 @@
         <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6756,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6799,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6813,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6829,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6894,7 +6889,7 @@
         <v>46006</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6950,7 +6945,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6964,10 +6959,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46154</v>
+        <v>45636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6975,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7018,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7037,10 +7032,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45217</v>
+        <v>46007</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7048,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.9</v>
+        <v>10.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7091,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7113,7 +7108,7 @@
         <v>46007</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7121,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7164,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7183,10 +7178,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7194,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7237,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7256,10 +7251,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7267,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>10.2</v>
+        <v>0.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7310,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7329,10 +7324,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46008</v>
+        <v>45078</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7340,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7383,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7397,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45685</v>
+        <v>46009</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7413,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7456,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7475,10 +7470,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45685</v>
+        <v>45229</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7491,7 +7486,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>11.1</v>
+        <v>5.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7534,7 +7529,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7548,10 +7543,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46008</v>
+        <v>45425</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7563,8 +7558,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.3</v>
+        <v>13.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45974</v>
+        <v>45181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45597</v>
+        <v>45671</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46155</v>
+        <v>45279</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45197</v>
+        <v>45405</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46009</v>
+        <v>45405</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44629</v>
+        <v>45642</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>13.3</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8055,14 +8055,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45044</v>
+        <v>46126</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45974</v>
+        <v>44957</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 52000-2021</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44463</v>
+        <v>45208</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 19135-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46009</v>
+        <v>46132</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8347,14 +8347,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45462</v>
+        <v>44908</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>11.1</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45974</v>
+        <v>45716</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>15.3</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 50257-2021</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44458</v>
+        <v>45716</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8573,7 +8573,7 @@
         <v>44813</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45076</v>
+        <v>45642</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>10.5</v>
+        <v>11.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45597</v>
+        <v>45642</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45278</v>
+        <v>44750</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8804,8 +8804,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8848,7 +8853,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8862,10 +8867,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45639</v>
+        <v>45603</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8878,7 +8883,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>10.3</v>
+        <v>2.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8921,7 +8926,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8935,10 +8940,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45103</v>
+        <v>45278</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8951,7 +8956,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8994,7 +8999,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9004,14 +9009,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45303</v>
+        <v>45873</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9024,7 +9029,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9067,7 +9072,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9081,10 +9086,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45369</v>
+        <v>44508</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9097,7 +9102,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>12.4</v>
+        <v>1.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9140,7 +9145,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9154,10 +9159,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44949</v>
+        <v>44482</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9170,7 +9175,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9213,7 +9218,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9227,10 +9232,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44508</v>
+        <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9243,7 +9248,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9286,7 +9291,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9300,10 +9305,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45256</v>
+        <v>46146</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9316,7 +9321,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9359,7 +9364,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9369,14 +9374,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45142</v>
+        <v>46146</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9389,7 +9394,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9449,7 +9454,7 @@
         <v>45671</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9505,7 +9510,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9519,10 +9524,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46073</v>
+        <v>46155</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9535,7 +9540,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9578,7 +9583,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9592,10 +9597,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45603</v>
+        <v>46154</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9608,7 +9613,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9651,7 +9656,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9661,14 +9666,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44908</v>
+        <v>45974</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9681,7 +9686,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9724,7 +9729,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9738,10 +9743,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44957</v>
+        <v>44817</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9754,7 +9759,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9797,7 +9802,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9811,10 +9816,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45642</v>
+        <v>45256</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9827,7 +9832,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9870,7 +9875,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9884,10 +9889,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45425</v>
+        <v>45462</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9899,13 +9904,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9948,7 +9948,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9962,10 +9962,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45553</v>
+        <v>45173</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>11.7</v>
+        <v>3.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10021,7 +10021,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45597</v>
+        <v>45173</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10094,7 +10094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10108,10 +10108,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45700</v>
+        <v>46009</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10167,7 +10167,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46200</v>
+        <v>45974</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10240,7 +10240,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45405</v>
+        <v>45974</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>15.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10313,7 +10313,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10330,7 +10330,7 @@
         <v>45405</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10386,7 +10386,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45415</v>
+        <v>44901</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>12.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10459,7 +10459,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10473,10 +10473,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45229</v>
+        <v>45415</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10532,7 +10532,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45129</v>
+        <v>45191</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>14.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10605,7 +10605,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 50257-2021</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46247</v>
+        <v>44458</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10678,7 +10678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10692,10 +10692,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45355</v>
+        <v>45217</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>27.1</v>
+        <v>4.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45636</v>
+        <v>45129</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>18.6</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10838,10 +10838,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44579</v>
+        <v>45590</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10897,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46206</v>
+        <v>44586</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.3</v>
+        <v>7.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45636</v>
+        <v>44949</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11043,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11060,7 +11060,7 @@
         <v>45103</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11116,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45099</v>
+        <v>46200</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45078</v>
+        <v>45229</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11272,14 +11272,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46253</v>
+        <v>45303</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11345,14 +11345,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45610</v>
+        <v>46247</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46258</v>
+        <v>46206</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44586</v>
+        <v>45180</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7.9</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45716</v>
+        <v>45355</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>27.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44928</v>
+        <v>46253</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45645</v>
+        <v>46258</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45181</v>
+        <v>45103</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45229</v>
+        <v>45700</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46272</v>
+        <v>45685</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>11.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46272</v>
+        <v>44902</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46269</v>
+        <v>45553</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>11.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45776</v>
+        <v>46272</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>8.4</v>
+        <v>2.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44889</v>
+        <v>46269</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45789</v>
+        <v>44907</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45789</v>
+        <v>46275</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45796</v>
+        <v>44928</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>10.9</v>
+        <v>3.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45209</v>
+        <v>44889</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45579</v>
+        <v>45776</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45068</v>
+        <v>45789</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45824</v>
+        <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>17.8</v>
+        <v>5.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45835</v>
+        <v>45796</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>10.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 1855-2025</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45671</v>
+        <v>44884</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -647,12 +647,122 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
+        <v>26</v>
+      </c>
+      <c r="U2" t="n">
+        <v>26</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gammelgransskål
+Vedskivlav
+Nästlav
+Vedticka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 1855-2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45671</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gammelgransskål
@@ -662,115 +772,115 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 41136-2023</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>45173</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E4" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>5.7</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S4" t="n">
         <v>6</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>26</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>26</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -780,145 +890,35 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 54858-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44884</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>26</v>
-      </c>
-      <c r="U4" t="n">
-        <v>26</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gammelgransskål
-Vedskivlav
-Nästlav
-Vedticka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 63800-2023</t>
+          <t>A 21714-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45278</v>
+        <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1099,155 +1099,155 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 63800-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Trana</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 21714-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52000-2021</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44463</v>
+        <v>45716</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44579</v>
+        <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45685</v>
+        <v>45173</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45099</v>
+        <v>45405</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45716</v>
+        <v>44901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>12.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45261</v>
+        <v>45103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45359</v>
+        <v>44872</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45076</v>
+        <v>45636</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45645</v>
+        <v>45590</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45209</v>
+        <v>45824</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>17.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45579</v>
+        <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45636</v>
+        <v>45581</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>18.6</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45636</v>
+        <v>45359</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45597</v>
+        <v>45835</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45068</v>
+        <v>45180</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.6</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44629</v>
+        <v>45581</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>13.3</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3604,7 +3604,7 @@
         <v>45894</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45824</v>
+        <v>44482</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>17.8</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45903</v>
+        <v>45645</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>10.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3816,14 +3816,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45903</v>
+        <v>46126</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 19135-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45835</v>
+        <v>46132</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45910</v>
+        <v>44750</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3981,8 +3981,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4030,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4044,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45581</v>
+        <v>45903</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4060,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4103,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4117,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45597</v>
+        <v>45903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4133,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4176,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4190,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45922</v>
+        <v>45910</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4206,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4249,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4263,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45922</v>
+        <v>46009</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4279,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>8.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4334,7 +4339,7 @@
         <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4390,7 +4395,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4409,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44872</v>
+        <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4425,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4468,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4482,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45597</v>
+        <v>45217</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4498,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4541,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4555,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45369</v>
+        <v>45685</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4571,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>12.4</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4614,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4628,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45936</v>
+        <v>45685</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4644,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>11.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4687,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4701,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45943</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4717,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4760,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4774,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45945</v>
+        <v>45873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4790,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4833,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4847,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45946</v>
+        <v>45197</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4863,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4906,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4920,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45946</v>
+        <v>44629</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4936,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>13.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4979,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4993,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45953</v>
+        <v>45044</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5009,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5052,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 50257-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5066,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45953</v>
+        <v>44458</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5082,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5125,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5139,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45520</v>
+        <v>44813</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5155,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5198,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5212,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45639</v>
+        <v>46146</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5228,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>10.3</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5271,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5285,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45103</v>
+        <v>46146</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5301,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5344,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5358,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45645</v>
+        <v>45597</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5374,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10.5</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5417,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5431,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45044</v>
+        <v>45278</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5447,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5490,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5495,14 +5500,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45197</v>
+        <v>45303</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5515,7 +5520,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5558,7 +5563,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5572,10 +5577,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45966</v>
+        <v>46154</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5588,7 +5593,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5631,7 +5636,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5645,10 +5650,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45968</v>
+        <v>45369</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5661,7 +5666,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>12.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5704,7 +5709,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5718,10 +5723,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45973</v>
+        <v>45936</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5734,7 +5739,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5777,7 +5782,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5791,10 +5796,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45973</v>
+        <v>44949</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5807,7 +5812,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5850,7 +5855,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5864,10 +5869,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45716</v>
+        <v>45974</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5880,7 +5885,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5923,7 +5928,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5937,10 +5942,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46073</v>
+        <v>46155</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5953,7 +5958,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5996,7 +6001,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45987</v>
+        <v>44508</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6026,7 +6031,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6086,7 +6091,7 @@
         <v>45142</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6142,7 +6147,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6156,10 +6161,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45987</v>
+        <v>45671</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6172,7 +6177,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6215,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6229,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45986</v>
+        <v>45974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6245,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6288,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6302,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45989</v>
+        <v>46009</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6318,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6361,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6375,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45581</v>
+        <v>45462</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6391,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>11.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6434,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6444,14 +6449,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45610</v>
+        <v>45974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6464,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.3</v>
+        <v>15.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6507,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6521,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46002</v>
+        <v>45603</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6537,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6580,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6594,10 +6599,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46002</v>
+        <v>45943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6610,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6663,14 +6668,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46002</v>
+        <v>44908</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6683,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6740,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46002</v>
+        <v>44957</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6756,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>9</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6799,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6813,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46007</v>
+        <v>45945</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6829,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6872,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6886,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46006</v>
+        <v>45946</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6902,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6945,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6959,10 +6964,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45636</v>
+        <v>45597</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6975,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7018,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7032,10 +7037,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46007</v>
+        <v>45946</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7048,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>10.2</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7091,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7105,10 +7110,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46007</v>
+        <v>45415</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7121,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7164,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7178,10 +7183,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46008</v>
+        <v>45129</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7194,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7237,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7251,10 +7256,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46008</v>
+        <v>45953</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7267,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7310,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7324,10 +7329,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45078</v>
+        <v>45953</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7340,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7383,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7397,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46009</v>
+        <v>45355</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7413,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>27.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7456,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7470,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45229</v>
+        <v>45636</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7486,7 +7491,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.7</v>
+        <v>18.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7529,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7543,10 +7548,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45425</v>
+        <v>44579</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7558,13 +7563,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>13.9</v>
+        <v>5.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45181</v>
+        <v>45636</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45671</v>
+        <v>45103</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45279</v>
+        <v>45078</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45405</v>
+        <v>45968</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45405</v>
+        <v>45966</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45642</v>
+        <v>45973</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8055,14 +8055,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46126</v>
+        <v>46200</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44957</v>
+        <v>45973</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45208</v>
+        <v>44586</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.3</v>
+        <v>7.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19135-2026</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46132</v>
+        <v>45716</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8347,14 +8347,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44908</v>
+        <v>46247</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45716</v>
+        <v>45645</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45716</v>
+        <v>46206</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44813</v>
+        <v>45181</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45642</v>
+        <v>45986</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>11.7</v>
+        <v>3.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44750</v>
+        <v>45642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8804,13 +8804,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>4.7</v>
+        <v>11.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8853,7 +8848,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8867,10 +8862,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45603</v>
+        <v>45642</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8883,7 +8878,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8926,7 +8921,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8940,10 +8935,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45278</v>
+        <v>45191</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8956,7 +8951,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>14.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8999,7 +8994,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9013,10 +9008,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45873</v>
+        <v>45987</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9029,7 +9024,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9072,7 +9067,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9086,10 +9081,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44508</v>
+        <v>45208</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9102,7 +9097,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9145,7 +9140,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9159,10 +9154,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44482</v>
+        <v>45987</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9175,7 +9170,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9218,7 +9213,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9232,10 +9227,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46009</v>
+        <v>46253</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9248,7 +9243,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9291,7 +9286,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9305,10 +9300,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46146</v>
+        <v>45989</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9321,7 +9316,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9364,7 +9359,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9378,10 +9373,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46146</v>
+        <v>44817</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9394,7 +9389,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9437,7 +9432,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9451,10 +9446,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45671</v>
+        <v>46258</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9467,7 +9462,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9510,7 +9505,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9524,10 +9519,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46155</v>
+        <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9540,7 +9535,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9583,7 +9578,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9597,10 +9592,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46154</v>
+        <v>46002</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9613,7 +9608,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9656,7 +9651,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9670,10 +9665,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45974</v>
+        <v>46002</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9686,7 +9681,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9729,7 +9724,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9743,10 +9738,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44817</v>
+        <v>46002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9759,7 +9754,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9802,7 +9797,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9816,10 +9811,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45256</v>
+        <v>46006</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9832,7 +9827,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9875,7 +9870,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9889,10 +9884,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45462</v>
+        <v>45279</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9905,7 +9900,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>11.1</v>
+        <v>3.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9948,7 +9943,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9962,10 +9957,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45173</v>
+        <v>45716</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9978,7 +9973,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10021,7 +10016,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10035,10 +10030,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45173</v>
+        <v>45716</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10051,7 +10046,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10094,7 +10089,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10108,10 +10103,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46009</v>
+        <v>46272</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10124,7 +10119,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10167,7 +10162,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10181,10 +10176,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45974</v>
+        <v>46007</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10197,7 +10192,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10240,7 +10235,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10254,10 +10249,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45974</v>
+        <v>46007</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10270,7 +10265,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>15.3</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10313,7 +10308,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10327,10 +10322,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45405</v>
+        <v>46007</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10386,7 +10381,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10400,10 +10395,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44901</v>
+        <v>46008</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10416,7 +10411,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>12.1</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10459,7 +10454,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10473,10 +10468,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45415</v>
+        <v>46008</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10489,7 +10484,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10532,7 +10527,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10546,10 +10541,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45191</v>
+        <v>46272</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10562,7 +10557,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>14.9</v>
+        <v>2.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10605,7 +10600,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 50257-2021</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10619,10 +10614,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44458</v>
+        <v>46269</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10635,7 +10630,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10678,7 +10673,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10692,10 +10687,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45217</v>
+        <v>45671</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10708,7 +10703,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10751,7 +10746,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10765,10 +10760,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45129</v>
+        <v>46009</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10781,7 +10776,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10824,7 +10819,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10838,10 +10833,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45590</v>
+        <v>44907</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,7 +10849,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10897,7 +10892,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10906,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44586</v>
+        <v>45261</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10922,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10965,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10979,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44949</v>
+        <v>45520</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11000,7 +10995,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>7.6</v>
+        <v>2.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11043,7 +11038,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11057,10 +11052,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45103</v>
+        <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11073,7 +11068,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11116,7 +11111,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11125,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46200</v>
+        <v>44902</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11141,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11184,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11198,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45229</v>
+        <v>45597</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11219,7 +11214,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11257,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 52000-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11272,14 +11267,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45303</v>
+        <v>44463</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11292,7 +11287,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11330,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11349,10 +11344,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46247</v>
+        <v>45076</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11360,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.3</v>
+        <v>10.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11403,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11417,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46206</v>
+        <v>45103</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11433,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11476,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11490,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45180</v>
+        <v>45256</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11506,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11549,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11563,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45355</v>
+        <v>45639</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11579,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>27.1</v>
+        <v>10.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11622,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11636,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46253</v>
+        <v>45642</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11652,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11695,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11709,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46258</v>
+        <v>45425</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11729,8 +11724,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>13.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45103</v>
+        <v>45553</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.3</v>
+        <v>11.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11863,7 +11863,7 @@
         <v>45700</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45685</v>
+        <v>45405</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>11.1</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44902</v>
+        <v>45405</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45553</v>
+        <v>45229</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>11.7</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46272</v>
+        <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12221,14 +12221,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46272</v>
+        <v>45610</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46269</v>
+        <v>44928</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44907</v>
+        <v>45776</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46275</v>
+        <v>44889</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.8</v>
+        <v>7.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44928</v>
+        <v>45789</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44889</v>
+        <v>45789</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>7.3</v>
+        <v>5.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45776</v>
+        <v>45796</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>8.4</v>
+        <v>10.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45789</v>
+        <v>45209</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45789</v>
+        <v>45579</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45796</v>
+        <v>45068</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>10.9</v>
+        <v>8.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 41136-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44884</v>
+        <v>45173</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -663,31 +663,31 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>45671</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49284-2022</t>
+          <t>A 28542-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44861</v>
+        <v>44748</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28542-2022</t>
+          <t>A 49284-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44748</v>
+        <v>44861</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 52000-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45716</v>
+        <v>44463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45173</v>
+        <v>45359</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45173</v>
+        <v>44579</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45405</v>
+        <v>45685</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44901</v>
+        <v>45099</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45103</v>
+        <v>45716</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44872</v>
+        <v>45261</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45636</v>
+        <v>45076</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45590</v>
+        <v>45645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45824</v>
+        <v>45636</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>17.8</v>
+        <v>18.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46073</v>
+        <v>45636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45581</v>
+        <v>45597</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45359</v>
+        <v>44629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>13.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45835</v>
+        <v>45581</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45180</v>
+        <v>45597</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45581</v>
+        <v>45597</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45894</v>
+        <v>44872</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44482</v>
+        <v>45369</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>12.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45645</v>
+        <v>45520</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10.5</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3816,14 +3816,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46126</v>
+        <v>45103</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19135-2026</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46132</v>
+        <v>45044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44750</v>
+        <v>45645</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3981,13 +3981,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4030,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4044,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45903</v>
+        <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4060,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4103,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4117,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45903</v>
+        <v>45716</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4133,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4176,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4186,14 +4181,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45910</v>
+        <v>45142</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4206,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4249,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4263,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46009</v>
+        <v>45581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4279,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4322,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4332,14 +4327,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45922</v>
+        <v>45610</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4352,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4395,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4409,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45922</v>
+        <v>45894</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4425,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4468,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4482,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45217</v>
+        <v>45903</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4498,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4541,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4555,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45685</v>
+        <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4571,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4614,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4628,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45685</v>
+        <v>45636</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4644,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>11.1</v>
+        <v>5.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4687,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4701,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>45873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4717,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4760,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4774,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45873</v>
+        <v>45910</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4790,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.9</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4833,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4847,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45197</v>
+        <v>46009</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4863,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4906,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4920,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44629</v>
+        <v>45078</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4936,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>13.3</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4979,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4993,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45044</v>
+        <v>45922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5009,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5052,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50257-2021</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5066,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44458</v>
+        <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5082,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5125,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5139,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44813</v>
+        <v>45922</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5155,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5198,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5212,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46146</v>
+        <v>45229</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5228,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5271,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5285,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46146</v>
+        <v>45425</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5300,8 +5295,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>13.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5358,10 +5358,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45597</v>
+        <v>45181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45278</v>
+        <v>45671</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5490,7 +5490,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5500,14 +5500,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45303</v>
+        <v>46146</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5577,10 +5577,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46154</v>
+        <v>45936</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5636,7 +5636,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45369</v>
+        <v>46146</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>12.4</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5709,7 +5709,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45936</v>
+        <v>45279</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5782,7 +5782,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44949</v>
+        <v>45943</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45974</v>
+        <v>45945</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>7.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46155</v>
+        <v>45405</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44508</v>
+        <v>45405</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6084,14 +6084,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45142</v>
+        <v>45642</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45671</v>
+        <v>45946</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>8.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45974</v>
+        <v>45946</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46009</v>
+        <v>44957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45462</v>
+        <v>45953</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>11.1</v>
+        <v>3.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45974</v>
+        <v>45953</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>15.3</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45603</v>
+        <v>45208</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6595,14 +6595,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45943</v>
+        <v>44908</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6668,14 +6668,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44908</v>
+        <v>45716</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44957</v>
+        <v>45716</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45945</v>
+        <v>44813</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45946</v>
+        <v>45966</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45597</v>
+        <v>46155</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45946</v>
+        <v>45968</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45415</v>
+        <v>45973</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45129</v>
+        <v>45973</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45953</v>
+        <v>46154</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45953</v>
+        <v>45642</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.7</v>
+        <v>11.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45355</v>
+        <v>45642</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>27.1</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45636</v>
+        <v>44750</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7490,8 +7490,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>18.6</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7534,7 +7539,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7548,10 +7553,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44579</v>
+        <v>45603</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7564,7 +7569,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7612,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7621,10 +7626,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45636</v>
+        <v>45987</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7642,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7685,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7699,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45103</v>
+        <v>45987</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7715,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7758,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7772,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45078</v>
+        <v>45974</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7788,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7831,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7840,10 +7845,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45968</v>
+        <v>45986</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7861,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7904,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7918,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45966</v>
+        <v>45989</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7934,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7977,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7991,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45973</v>
+        <v>45278</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8007,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8050,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8059,10 +8064,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46200</v>
+        <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8075,7 +8080,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8123,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8137,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45973</v>
+        <v>44482</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8153,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8196,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8210,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44586</v>
+        <v>45462</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8226,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.9</v>
+        <v>11.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8269,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8283,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45716</v>
+        <v>46002</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8299,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8342,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8356,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46247</v>
+        <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8372,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8415,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8429,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45645</v>
+        <v>46002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8445,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8488,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8502,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46206</v>
+        <v>46009</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8518,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8561,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8575,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45181</v>
+        <v>45974</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8591,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8634,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8648,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45986</v>
+        <v>46002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8659,7 +8664,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8707,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8721,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45229</v>
+        <v>46007</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8737,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8780,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8794,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45642</v>
+        <v>46006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8805,7 +8810,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>11.7</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8848,7 +8853,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8862,10 +8867,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45642</v>
+        <v>46007</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8878,7 +8883,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8921,7 +8926,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8935,10 +8940,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45191</v>
+        <v>46007</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8951,7 +8956,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>14.9</v>
+        <v>3.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8994,7 +8999,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9008,10 +9013,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45987</v>
+        <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9024,7 +9029,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.9</v>
+        <v>15.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9067,7 +9072,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9081,10 +9086,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45208</v>
+        <v>46008</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9097,7 +9102,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9140,7 +9145,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9154,10 +9159,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45987</v>
+        <v>46008</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9170,7 +9175,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9213,7 +9218,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9227,10 +9232,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46253</v>
+        <v>45671</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9243,7 +9248,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9286,7 +9291,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9300,10 +9305,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45989</v>
+        <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9316,7 +9321,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9376,7 +9381,7 @@
         <v>44817</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9432,7 +9437,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9446,10 +9451,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46258</v>
+        <v>45256</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9462,7 +9467,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9505,7 +9510,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9519,10 +9524,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>45173</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9535,7 +9540,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9578,7 +9583,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9592,10 +9597,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46002</v>
+        <v>45173</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9608,7 +9613,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9651,7 +9656,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9665,10 +9670,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46002</v>
+        <v>45405</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9681,7 +9686,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9724,7 +9729,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9738,10 +9743,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46002</v>
+        <v>44901</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9754,7 +9759,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>12.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9797,7 +9802,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9811,10 +9816,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46006</v>
+        <v>45639</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9827,7 +9832,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4</v>
+        <v>10.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9870,7 +9875,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9884,10 +9889,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45279</v>
+        <v>45415</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9900,7 +9905,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9943,7 +9948,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9957,10 +9962,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45716</v>
+        <v>45191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9973,7 +9978,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>14.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10016,7 +10021,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 50257-2021</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10030,10 +10035,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45716</v>
+        <v>44458</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10046,7 +10051,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10089,7 +10094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10103,10 +10108,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46272</v>
+        <v>46073</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10119,7 +10124,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10162,7 +10167,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10176,10 +10181,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46007</v>
+        <v>45217</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10192,7 +10197,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10235,7 +10240,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10249,10 +10254,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46007</v>
+        <v>45129</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10265,7 +10270,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10308,7 +10313,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10322,10 +10327,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46007</v>
+        <v>45590</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10338,7 +10343,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>10.2</v>
+        <v>7.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10381,7 +10386,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10395,10 +10400,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46008</v>
+        <v>44586</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10411,7 +10416,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10454,7 +10459,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10468,10 +10473,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46008</v>
+        <v>44949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10484,7 +10489,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.3</v>
+        <v>7.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10527,7 +10532,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10541,10 +10546,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46272</v>
+        <v>45103</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10557,7 +10562,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10600,7 +10605,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10614,10 +10619,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46269</v>
+        <v>45229</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10630,7 +10635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10673,7 +10678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10683,14 +10688,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45671</v>
+        <v>45303</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10703,7 +10708,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10746,7 +10751,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10760,10 +10765,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46009</v>
+        <v>46200</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10776,7 +10781,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10819,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10829,14 +10834,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44907</v>
+        <v>46126</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10849,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10892,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10906,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45261</v>
+        <v>45180</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10922,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10965,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 19135-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10979,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45520</v>
+        <v>46132</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -10995,7 +11000,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11038,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11052,10 +11057,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46275</v>
+        <v>45355</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11068,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.8</v>
+        <v>27.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11111,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11125,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44902</v>
+        <v>46247</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11141,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11184,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11198,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45597</v>
+        <v>46206</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11214,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11257,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 52000-2021</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11271,10 +11276,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44463</v>
+        <v>46253</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11287,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11330,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11344,10 +11349,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45076</v>
+        <v>45103</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11360,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>10.5</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11403,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11417,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45103</v>
+        <v>45700</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11433,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11476,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11490,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45256</v>
+        <v>45685</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11506,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>11.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11549,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11563,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45639</v>
+        <v>46258</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11579,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>10.3</v>
+        <v>3.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11622,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11636,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45642</v>
+        <v>44902</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11652,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11695,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11709,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45425</v>
+        <v>45553</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11724,13 +11729,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>13.9</v>
+        <v>11.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45553</v>
+        <v>44907</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>11.7</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45700</v>
+        <v>44928</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45405</v>
+        <v>44889</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45405</v>
+        <v>45776</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>8.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45229</v>
+        <v>46272</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45099</v>
+        <v>46272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12221,14 +12221,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45610</v>
+        <v>46269</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44928</v>
+        <v>46275</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45776</v>
+        <v>45789</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44889</v>
+        <v>45789</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45789</v>
+        <v>45796</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.7</v>
+        <v>10.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45789</v>
+        <v>45209</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45796</v>
+        <v>45579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>10.9</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45209</v>
+        <v>45068</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.2</v>
+        <v>8.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45579</v>
+        <v>45824</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.8</v>
+        <v>17.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45068</v>
+        <v>45835</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>8.6</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45173</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45671</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44748</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44861</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45359</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>44579</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>45685</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45099</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45716</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45261</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45076</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>45636</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>45597</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>45581</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>45597</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45597</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>44872</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>45369</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45520</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>45103</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>45645</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45716</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45142</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45610</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45894</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45903</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>45636</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45910</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>46009</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45078</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45922</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>45229</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45425</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>45181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45671</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>46146</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45936</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>46146</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45279</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>45943</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>45945</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>45405</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>45405</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>45642</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>45946</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45946</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45953</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45953</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45208</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44908</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45716</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45716</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44813</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45966</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>46155</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45968</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45973</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45973</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>46154</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45642</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45642</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>44750</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45603</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45987</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45987</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45974</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45986</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45989</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45278</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44482</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45462</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>46002</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>46002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>46009</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45974</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>46002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>46007</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>46006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>46007</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>46007</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>46008</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>46008</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>45671</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44817</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45256</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45173</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45173</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>45405</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44901</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45639</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>45415</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>45191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>44458</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>46073</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45217</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45129</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45590</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44586</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45103</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>45229</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>45303</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>46200</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>46126</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45180</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>46132</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>45355</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>46247</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>46206</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>46253</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>45103</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>45700</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45685</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>46258</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>44902</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>45553</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44907</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44928</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44889</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>45776</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>46272</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>46272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>46269</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>46275</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>45789</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45789</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>45796</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>45209</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45068</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>45824</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45835</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45173</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45671</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28542-2022</t>
+          <t>A 49284-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44748</v>
+        <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49284-2022</t>
+          <t>A 28542-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44861</v>
+        <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45359</v>
+        <v>44579</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44579</v>
+        <v>45685</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45685</v>
+        <v>45099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45099</v>
+        <v>45261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45716</v>
+        <v>45359</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45261</v>
+        <v>45716</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
         <v>45076</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>45636</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>45597</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>45581</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>45597</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45597</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>44872</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>45369</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45520</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>45103</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45044</v>
+        <v>45645</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45645</v>
+        <v>45044</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4042,7 +4042,7 @@
         <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45716</v>
+        <v>45894</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4181,14 +4181,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45142</v>
+        <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45581</v>
+        <v>45903</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4327,14 +4327,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45610</v>
+        <v>45716</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45894</v>
+        <v>45910</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45903</v>
+        <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45903</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45636</v>
+        <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4692,14 +4692,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45873</v>
+        <v>45142</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45910</v>
+        <v>45581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4838,14 +4838,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46009</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.1</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45078</v>
+        <v>45873</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45922</v>
+        <v>46009</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45922</v>
+        <v>45936</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45922</v>
+        <v>46146</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45229</v>
+        <v>46146</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45425</v>
+        <v>45636</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5295,13 +5295,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>13.9</v>
+        <v>5.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5344,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5358,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45181</v>
+        <v>45943</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5374,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5417,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5431,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45671</v>
+        <v>46155</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5447,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5490,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5504,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46146</v>
+        <v>45945</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5520,7 +5515,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5563,7 +5558,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5577,10 +5572,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45936</v>
+        <v>46154</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5593,7 +5588,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5636,7 +5631,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5650,10 +5645,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46146</v>
+        <v>45946</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5666,7 +5661,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5709,7 +5704,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5723,10 +5718,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45279</v>
+        <v>45946</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5739,7 +5734,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5782,7 +5777,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5796,10 +5791,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45943</v>
+        <v>45078</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5807,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5850,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45945</v>
+        <v>45953</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5880,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5923,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5942,10 +5937,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45405</v>
+        <v>45974</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5953,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +5996,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45405</v>
+        <v>45953</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6026,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6069,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6088,10 +6083,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6104,7 +6099,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6147,7 +6142,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6161,10 +6156,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45946</v>
+        <v>45425</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6176,8 +6171,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>8.5</v>
+        <v>13.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45946</v>
+        <v>45181</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44957</v>
+        <v>45966</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45953</v>
+        <v>45968</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45953</v>
+        <v>45973</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45208</v>
+        <v>45973</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6595,14 +6595,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44908</v>
+        <v>45462</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>11.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45716</v>
+        <v>46009</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45716</v>
+        <v>45974</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44813</v>
+        <v>45974</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.5</v>
+        <v>15.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45966</v>
+        <v>45279</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46155</v>
+        <v>45405</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45968</v>
+        <v>45405</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45973</v>
+        <v>45642</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45973</v>
+        <v>45987</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46154</v>
+        <v>45987</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45642</v>
+        <v>44957</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>11.7</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45642</v>
+        <v>45986</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44750</v>
+        <v>45989</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7490,13 +7490,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7539,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7553,10 +7548,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45603</v>
+        <v>45208</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7569,7 +7564,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7612,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7622,14 +7617,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45987</v>
+        <v>44908</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7642,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7685,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7699,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45987</v>
+        <v>45716</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7715,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7758,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7772,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45974</v>
+        <v>45716</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7788,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7831,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7845,10 +7840,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45986</v>
+        <v>44813</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7861,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7904,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7918,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45989</v>
+        <v>46002</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7934,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7977,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7991,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45278</v>
+        <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8007,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8050,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8064,10 +8059,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44508</v>
+        <v>46002</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8080,7 +8075,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8123,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8137,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44482</v>
+        <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8153,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8196,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8210,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45462</v>
+        <v>46007</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8226,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>11.1</v>
+        <v>4.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8269,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8283,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8299,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8342,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8356,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8372,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>10.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8415,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8429,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8445,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8488,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8502,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46009</v>
+        <v>46008</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8518,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8561,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8575,10 +8570,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45974</v>
+        <v>46008</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8591,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8634,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8648,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46002</v>
+        <v>45642</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8664,7 +8659,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>9</v>
+        <v>11.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8707,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8721,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46007</v>
+        <v>45642</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8737,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8780,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8794,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46006</v>
+        <v>44750</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8809,8 +8804,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8853,7 +8853,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>10.2</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8926,7 +8926,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8940,10 +8940,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46007</v>
+        <v>45603</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8999,7 +8999,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9013,10 +9013,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45974</v>
+        <v>45278</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>15.3</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46008</v>
+        <v>44508</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9145,7 +9145,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9159,10 +9159,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46008</v>
+        <v>44482</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45671</v>
+        <v>45639</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>10.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9291,7 +9291,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9305,10 +9305,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46009</v>
+        <v>46073</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9364,7 +9364,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9378,10 +9378,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44817</v>
+        <v>45671</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45256</v>
+        <v>46200</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9510,7 +9510,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9524,10 +9524,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45173</v>
+        <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9583,7 +9583,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9597,10 +9597,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45173</v>
+        <v>45256</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9656,7 +9656,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45405</v>
+        <v>46247</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9729,7 +9729,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44901</v>
+        <v>45173</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>12.1</v>
+        <v>3.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9802,7 +9802,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9816,10 +9816,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45639</v>
+        <v>45173</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>10.3</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9875,7 +9875,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45415</v>
+        <v>45405</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9948,7 +9948,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9962,10 +9962,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45191</v>
+        <v>44901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>14.9</v>
+        <v>12.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10021,7 +10021,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 50257-2021</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44458</v>
+        <v>46206</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10094,7 +10094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10104,14 +10104,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46073</v>
+        <v>46126</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10167,7 +10167,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45217</v>
+        <v>45415</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10240,7 +10240,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 19135-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45129</v>
+        <v>46132</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10313,7 +10313,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10327,10 +10327,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45590</v>
+        <v>45191</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.5</v>
+        <v>14.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10386,7 +10386,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44586</v>
+        <v>45217</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7.9</v>
+        <v>4.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10459,7 +10459,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10473,10 +10473,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44949</v>
+        <v>45129</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.6</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10532,7 +10532,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45103</v>
+        <v>46253</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10605,7 +10605,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45229</v>
+        <v>45590</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10678,7 +10678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10688,14 +10688,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45303</v>
+        <v>44586</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>7.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46200</v>
+        <v>46258</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10834,14 +10834,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46126</v>
+        <v>44949</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10897,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45180</v>
+        <v>45103</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19135-2026</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46132</v>
+        <v>45229</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11043,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11053,14 +11053,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45355</v>
+        <v>45303</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>27.1</v>
+        <v>1.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11116,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46247</v>
+        <v>45180</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46206</v>
+        <v>45355</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>27.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46253</v>
+        <v>46272</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11349,10 +11349,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45103</v>
+        <v>46272</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45700</v>
+        <v>46269</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45685</v>
+        <v>46275</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>11.1</v>
+        <v>2.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46258</v>
+        <v>45103</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44902</v>
+        <v>45700</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45553</v>
+        <v>45685</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44907</v>
+        <v>45671</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11856,14 +11856,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44928</v>
+        <v>46286</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44889</v>
+        <v>44902</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45776</v>
+        <v>45553</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8.4</v>
+        <v>11.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46272</v>
+        <v>44907</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46272</v>
+        <v>44928</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46269</v>
+        <v>44889</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46275</v>
+        <v>45776</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12374,7 +12374,7 @@
         <v>45789</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45789</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>45796</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>45209</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45068</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>45824</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45835</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE168"/>
+  <dimension ref="A1:AE169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -663,31 +663,31 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>45671</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 41136-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44884</v>
+        <v>45173</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 21714-2026</t>
+          <t>A 63800-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46149</v>
+        <v>45278</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1099,155 +1099,155 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 21714-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Rödvingetrast</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 63800-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45278</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Trana</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47661-2022</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44854</v>
+        <v>44750</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2229,8 +2229,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>9.9</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2273,7 +2278,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60754-2021</t>
+          <t>A 47661-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2287,10 +2292,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44496</v>
+        <v>44854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2303,7 +2308,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>9.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2346,7 +2351,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 71446-2021</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2365,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44540</v>
+        <v>45789</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2381,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2424,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52000-2021</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2438,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44463</v>
+        <v>45789</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2454,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2497,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 60754-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2511,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44579</v>
+        <v>44496</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2527,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2570,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 71446-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2584,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45685</v>
+        <v>44540</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2600,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2643,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2657,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45099</v>
+        <v>45217</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2673,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2716,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2730,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45261</v>
+        <v>45685</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2746,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2789,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2803,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45359</v>
+        <v>45685</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2819,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>11.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2862,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2874,7 +2879,7 @@
         <v>45716</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2892,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2935,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2949,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45076</v>
+        <v>45173</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2965,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3008,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3022,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45645</v>
+        <v>45173</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3038,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3081,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3095,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45636</v>
+        <v>45197</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3111,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>18.6</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3154,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3168,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45636</v>
+        <v>45405</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3184,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3227,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3241,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45597</v>
+        <v>44629</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3257,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>13.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3300,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3314,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44629</v>
+        <v>45044</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3330,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>13.3</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3373,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3387,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45581</v>
+        <v>44813</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3403,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3446,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3460,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45597</v>
+        <v>44901</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3476,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>12.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3519,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3533,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45597</v>
+        <v>45796</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3549,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>10.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3592,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3606,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44872</v>
+        <v>45103</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3622,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3665,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3679,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45369</v>
+        <v>45597</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3695,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>12.4</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3738,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3752,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45520</v>
+        <v>45278</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3768,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3811,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3825,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45103</v>
+        <v>45894</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3841,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3884,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3889,14 +3894,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45645</v>
+        <v>45303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3914,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3957,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3971,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45044</v>
+        <v>45369</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3987,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.8</v>
+        <v>12.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4030,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4044,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45197</v>
+        <v>45209</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4060,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4103,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4117,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45894</v>
+        <v>44949</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4133,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4176,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4190,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45903</v>
+        <v>45579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4206,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4249,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4263,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45903</v>
+        <v>44508</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4279,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4322,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4327,14 +4332,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45716</v>
+        <v>45142</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4352,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4395,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4409,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45910</v>
+        <v>45671</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4425,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4468,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4482,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45922</v>
+        <v>45903</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4498,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4541,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4555,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4571,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4614,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4628,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45922</v>
+        <v>45910</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4644,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4687,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4692,14 +4697,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45142</v>
+        <v>45603</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4717,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4760,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4765,14 +4770,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45581</v>
+        <v>44908</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4790,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4833,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4838,14 +4843,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>44957</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4863,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4906,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4920,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45873</v>
+        <v>44872</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4936,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4979,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4993,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46009</v>
+        <v>45922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5009,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5052,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5066,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45936</v>
+        <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5082,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5125,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5139,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46146</v>
+        <v>45636</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5155,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5198,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5212,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46146</v>
+        <v>45597</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5228,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5271,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5285,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45636</v>
+        <v>45922</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5301,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5344,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5358,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45943</v>
+        <v>45590</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5374,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5417,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5431,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46155</v>
+        <v>45068</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5447,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5490,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,10 +5504,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45945</v>
+        <v>45415</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5515,7 +5520,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5558,7 +5563,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5572,10 +5577,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46154</v>
+        <v>45936</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5588,7 +5593,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5631,7 +5636,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5645,10 +5650,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45946</v>
+        <v>45129</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5661,7 +5666,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5704,7 +5709,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5718,10 +5723,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45946</v>
+        <v>45355</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5734,7 +5739,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>27.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5777,7 +5782,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5791,10 +5796,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45078</v>
+        <v>45636</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5807,7 +5812,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>18.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5850,7 +5855,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5864,10 +5869,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45953</v>
+        <v>45943</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5880,7 +5885,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5923,7 +5928,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5937,10 +5942,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45974</v>
+        <v>44579</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5953,7 +5958,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5996,7 +6001,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45953</v>
+        <v>45945</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6026,7 +6031,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.6</v>
+        <v>7.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6069,7 +6074,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6083,10 +6088,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45229</v>
+        <v>45946</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6099,7 +6104,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6142,7 +6147,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6156,10 +6161,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45425</v>
+        <v>45946</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6171,13 +6176,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>13.9</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45181</v>
+        <v>45636</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45966</v>
+        <v>45581</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45968</v>
+        <v>45103</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45973</v>
+        <v>45078</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45973</v>
+        <v>45359</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45462</v>
+        <v>45953</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>11.1</v>
+        <v>3.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46009</v>
+        <v>45953</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45974</v>
+        <v>44586</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45974</v>
+        <v>45716</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>15.3</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45279</v>
+        <v>45180</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45405</v>
+        <v>45968</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45405</v>
+        <v>45966</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45642</v>
+        <v>45973</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45987</v>
+        <v>45973</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45987</v>
+        <v>45645</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44957</v>
+        <v>45824</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>17.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45986</v>
+        <v>45181</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45989</v>
+        <v>45581</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7534,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45208</v>
+        <v>45229</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7617,14 +7617,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44908</v>
+        <v>44482</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45716</v>
+        <v>45986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45716</v>
+        <v>45645</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44813</v>
+        <v>45642</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.5</v>
+        <v>11.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46002</v>
+        <v>45642</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46002</v>
+        <v>45987</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46002</v>
+        <v>45987</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46002</v>
+        <v>45191</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>9</v>
+        <v>14.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46007</v>
+        <v>45989</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46006</v>
+        <v>45208</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46007</v>
+        <v>44817</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>10.2</v>
+        <v>3.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45642</v>
+        <v>46002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45642</v>
+        <v>45835</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44750</v>
+        <v>46006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8804,13 +8804,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8853,7 +8848,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8867,10 +8862,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8883,7 +8878,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8926,7 +8921,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8940,10 +8935,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45603</v>
+        <v>46007</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8956,7 +8951,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8999,7 +8994,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9013,10 +9008,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45278</v>
+        <v>46007</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9029,7 +9024,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>10.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9072,7 +9067,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9086,10 +9081,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44508</v>
+        <v>46008</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9102,7 +9097,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9145,7 +9140,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9159,10 +9154,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44482</v>
+        <v>46008</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9175,7 +9170,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.4</v>
+        <v>0.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9218,7 +9213,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9232,10 +9227,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45639</v>
+        <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9248,7 +9243,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>10.3</v>
+        <v>0.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9291,7 +9286,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9305,10 +9300,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46073</v>
+        <v>45279</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9321,7 +9316,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9364,7 +9359,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9381,7 +9376,7 @@
         <v>45671</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9394,7 +9389,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9437,7 +9432,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9451,10 +9446,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46200</v>
+        <v>45716</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9467,7 +9462,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9510,7 +9505,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9524,10 +9519,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44817</v>
+        <v>45716</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9540,7 +9535,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9583,7 +9578,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9593,14 +9588,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45256</v>
+        <v>46286</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9613,7 +9608,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9656,7 +9651,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9670,10 +9665,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46247</v>
+        <v>45639</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9686,7 +9681,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>10.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9729,7 +9724,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9743,10 +9738,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45173</v>
+        <v>44907</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9759,7 +9754,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9802,7 +9797,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9816,10 +9811,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45173</v>
+        <v>45261</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9832,7 +9827,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9875,7 +9870,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9889,10 +9884,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45405</v>
+        <v>45520</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9905,7 +9900,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9948,7 +9943,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9962,10 +9957,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44901</v>
+        <v>46073</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9978,7 +9973,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>12.1</v>
+        <v>4.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10021,7 +10016,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 39269-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10035,10 +10030,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46206</v>
+        <v>46288</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10051,7 +10046,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10094,7 +10089,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 39266-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10104,14 +10099,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46126</v>
+        <v>46288</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10124,7 +10119,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10167,7 +10162,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10181,10 +10176,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45415</v>
+        <v>44902</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10197,7 +10192,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10240,7 +10235,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19135-2026</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10254,10 +10249,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46132</v>
+        <v>45597</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10270,7 +10265,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10313,7 +10308,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 52000-2021</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10327,10 +10322,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45191</v>
+        <v>44463</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>14.9</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10386,7 +10381,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10400,10 +10395,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45217</v>
+        <v>45076</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10416,7 +10411,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10459,7 +10454,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10473,10 +10468,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45129</v>
+        <v>45103</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10489,7 +10484,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10532,7 +10527,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10546,10 +10541,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46253</v>
+        <v>45256</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10562,7 +10557,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10605,7 +10600,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10615,14 +10610,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45590</v>
+        <v>46126</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10635,7 +10630,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10678,7 +10673,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10692,10 +10687,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44586</v>
+        <v>45642</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10708,7 +10703,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>7.9</v>
+        <v>2.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10751,7 +10746,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10765,10 +10760,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46258</v>
+        <v>45425</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10780,8 +10775,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>3.1</v>
+        <v>13.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10838,10 +10838,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44949</v>
+        <v>45553</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7.6</v>
+        <v>11.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10897,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45103</v>
+        <v>45700</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45229</v>
+        <v>45405</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11043,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11053,14 +11053,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45303</v>
+        <v>45405</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11116,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45180</v>
+        <v>45229</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45355</v>
+        <v>45099</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>27.1</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46272</v>
+        <v>46009</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11345,14 +11345,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46272</v>
+        <v>45610</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46269</v>
+        <v>44928</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46275</v>
+        <v>45873</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.8</v>
+        <v>6.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45103</v>
+        <v>46146</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45700</v>
+        <v>46146</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45685</v>
+        <v>45776</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>11.1</v>
+        <v>8.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45671</v>
+        <v>44889</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 38860-2026</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11856,14 +11856,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46286</v>
+        <v>46154</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44902</v>
+        <v>45974</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45553</v>
+        <v>46155</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44907</v>
+        <v>45974</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44928</v>
+        <v>46009</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44889</v>
+        <v>45462</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45776</v>
+        <v>45974</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>8.4</v>
+        <v>15.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45789</v>
+        <v>46200</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45789</v>
+        <v>46247</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45796</v>
+        <v>46206</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>10.9</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45209</v>
+        <v>46253</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45579</v>
+        <v>46258</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45068</v>
+        <v>46272</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8.6</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45824</v>
+        <v>46272</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>17.8</v>
+        <v>2.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45835</v>
+        <v>46269</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12938,78 +12938,151 @@
       </c>
       <c r="V167" s="2" t="inlineStr"/>
     </row>
-    <row r="168">
+    <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
+          <t>A 37395-2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E168" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
           <t>S 1664-2025</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D168" s="1" t="n">
+      <c r="D169" s="1" t="n">
         <v>45803</v>
       </c>
-      <c r="E168" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I168" t="n">
+      <c r="E169" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
         <v>7.8</v>
       </c>
-      <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" t="n">
-        <v>0</v>
-      </c>
-      <c r="M168" t="n">
-        <v>0</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0</v>
-      </c>
-      <c r="O168" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
-      </c>
-      <c r="S168" t="n">
-        <v>0</v>
-      </c>
-      <c r="T168" t="n">
-        <v>0</v>
-      </c>
-      <c r="U168" t="n">
-        <v>0</v>
-      </c>
-      <c r="V168" s="2" t="inlineStr"/>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE169"/>
+  <dimension ref="A1:AE168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 41136-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44884</v>
+        <v>45173</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -663,31 +663,31 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>45671</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 63800-2023</t>
+          <t>A 21714-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45278</v>
+        <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1099,155 +1099,155 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 63800-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Trana</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 21714-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 47661-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44750</v>
+        <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2229,13 +2229,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>9.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2278,7 +2273,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 47661-2022</t>
+          <t>A 60754-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2292,10 +2287,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44854</v>
+        <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2308,7 +2303,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>9.9</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2351,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 71446-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2365,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45789</v>
+        <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2381,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2424,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2438,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45789</v>
+        <v>45359</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2454,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2497,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60754-2021</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2511,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44496</v>
+        <v>44579</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2527,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2570,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 71446-2021</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2584,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44540</v>
+        <v>45685</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2600,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2643,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2657,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45217</v>
+        <v>45099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2673,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2716,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2730,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45685</v>
+        <v>45716</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2746,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2789,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2803,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45685</v>
+        <v>45261</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2819,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>11.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2862,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2876,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45716</v>
+        <v>45076</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2892,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2935,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2949,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45173</v>
+        <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2965,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3008,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3022,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45173</v>
+        <v>45636</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3038,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>18.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3081,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3095,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45197</v>
+        <v>45636</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3111,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3154,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3168,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45405</v>
+        <v>45597</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3184,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3244,7 +3239,7 @@
         <v>44629</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3300,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3314,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45044</v>
+        <v>45581</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3330,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3373,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3387,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44813</v>
+        <v>45597</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3403,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3446,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3460,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44901</v>
+        <v>45597</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3476,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3519,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3533,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45796</v>
+        <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3549,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10.9</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3592,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3606,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45103</v>
+        <v>45369</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3622,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>12.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3665,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3679,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45597</v>
+        <v>45520</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3695,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3738,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3752,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45278</v>
+        <v>45103</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3811,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3825,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45894</v>
+        <v>45645</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3841,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>10.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3884,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3894,14 +3889,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45303</v>
+        <v>45044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3914,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3957,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3971,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45369</v>
+        <v>45894</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3987,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>12.4</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4030,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4044,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45209</v>
+        <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4060,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4103,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4117,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44949</v>
+        <v>45903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4133,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4176,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4190,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45579</v>
+        <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4206,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4249,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4263,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44508</v>
+        <v>45716</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4279,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4322,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4332,14 +4327,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45142</v>
+        <v>45910</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4352,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4395,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4405,14 +4400,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45671</v>
+        <v>45142</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4425,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4468,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4482,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45903</v>
+        <v>45581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4498,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4541,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4555,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45903</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4571,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4614,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4628,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45910</v>
+        <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4644,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4687,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4701,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45603</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4717,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4760,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4774,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44908</v>
+        <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4790,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4833,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4847,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44957</v>
+        <v>45936</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4863,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4906,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4920,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44872</v>
+        <v>45636</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4936,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4979,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4993,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45922</v>
+        <v>45943</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5009,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5052,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5066,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45922</v>
+        <v>45945</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5082,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5125,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5139,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45636</v>
+        <v>45078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5155,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5198,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5212,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45597</v>
+        <v>45946</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5228,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5271,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5285,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45922</v>
+        <v>45946</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5301,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5344,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5358,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45590</v>
+        <v>45953</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5374,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5417,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5431,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45068</v>
+        <v>45229</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5447,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5490,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5504,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45415</v>
+        <v>45953</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5520,7 +5515,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5563,7 +5558,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5577,10 +5572,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45936</v>
+        <v>45425</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5592,8 +5587,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>13.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5636,7 +5636,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45129</v>
+        <v>45181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5709,7 +5709,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45355</v>
+        <v>45873</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>27.1</v>
+        <v>6.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5782,7 +5782,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45636</v>
+        <v>45966</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>18.6</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45943</v>
+        <v>46009</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.6</v>
+        <v>8.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44579</v>
+        <v>45968</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45945</v>
+        <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45946</v>
+        <v>45973</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.5</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45946</v>
+        <v>45973</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45636</v>
+        <v>45405</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45581</v>
+        <v>45405</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45103</v>
+        <v>45642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45078</v>
+        <v>44957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45359</v>
+        <v>45987</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45953</v>
+        <v>45208</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45953</v>
+        <v>45987</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44586</v>
+        <v>45986</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.9</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45716</v>
+        <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45180</v>
+        <v>46146</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6960,14 +6960,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45968</v>
+        <v>44908</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45966</v>
+        <v>45716</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45973</v>
+        <v>45716</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45973</v>
+        <v>46146</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45645</v>
+        <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45824</v>
+        <v>46155</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>17.8</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45181</v>
+        <v>46002</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45581</v>
+        <v>46154</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7534,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45229</v>
+        <v>46002</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44482</v>
+        <v>46002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45986</v>
+        <v>46002</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45645</v>
+        <v>46007</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45642</v>
+        <v>46006</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>11.7</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45642</v>
+        <v>46007</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45987</v>
+        <v>45974</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45987</v>
+        <v>46007</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45191</v>
+        <v>46008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>14.9</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45989</v>
+        <v>45642</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45208</v>
+        <v>45642</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44817</v>
+        <v>44750</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8366,8 +8366,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8415,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8429,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8445,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8488,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8502,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46002</v>
+        <v>45603</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8518,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8561,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8575,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8591,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8634,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8648,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46002</v>
+        <v>45278</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8659,7 +8664,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8707,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8721,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45835</v>
+        <v>44508</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8737,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8780,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8794,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46006</v>
+        <v>44482</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8805,7 +8810,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8848,7 +8853,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8862,10 +8867,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46007</v>
+        <v>45462</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8878,7 +8883,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.2</v>
+        <v>11.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8921,7 +8926,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8935,10 +8940,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8951,7 +8956,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8994,7 +8999,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9008,10 +9013,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46007</v>
+        <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9024,7 +9029,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>10.2</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9067,7 +9072,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9081,10 +9086,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46008</v>
+        <v>45974</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9097,7 +9102,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>15.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9140,7 +9145,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9154,10 +9159,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46008</v>
+        <v>45639</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9170,7 +9175,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.3</v>
+        <v>10.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9213,7 +9218,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9227,10 +9232,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46009</v>
+        <v>45671</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9243,7 +9248,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9286,7 +9291,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9300,10 +9305,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45279</v>
+        <v>46073</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9316,7 +9321,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9359,7 +9364,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9373,10 +9378,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45671</v>
+        <v>44817</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9389,7 +9394,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9432,7 +9437,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9446,10 +9451,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45716</v>
+        <v>45256</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9462,7 +9467,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9505,7 +9510,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9519,10 +9524,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45716</v>
+        <v>45173</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9535,7 +9540,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9578,7 +9583,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38860-2026</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9588,14 +9593,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46286</v>
+        <v>45173</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9608,7 +9613,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9651,7 +9656,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9665,10 +9670,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45639</v>
+        <v>45405</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9681,7 +9686,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>10.3</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9724,7 +9729,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9738,10 +9743,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44907</v>
+        <v>44901</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9754,7 +9759,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>12.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9797,7 +9802,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9811,10 +9816,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45261</v>
+        <v>45415</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9827,7 +9832,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>9.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9870,7 +9875,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9880,14 +9885,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45520</v>
+        <v>46126</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9900,7 +9905,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9943,7 +9948,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9957,10 +9962,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46073</v>
+        <v>45191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9973,7 +9978,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.1</v>
+        <v>14.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10016,7 +10021,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 39269-2026</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10030,10 +10035,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46288</v>
+        <v>45217</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10046,7 +10051,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10089,7 +10094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 39266-2026</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10103,10 +10108,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46288</v>
+        <v>45129</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10119,7 +10124,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10162,7 +10167,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10176,10 +10181,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44902</v>
+        <v>45590</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10192,7 +10197,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10235,7 +10240,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10249,10 +10254,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45597</v>
+        <v>44586</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10265,7 +10270,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10308,7 +10313,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 52000-2021</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10322,10 +10327,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44463</v>
+        <v>46200</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10338,7 +10343,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10381,7 +10386,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10395,10 +10400,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45076</v>
+        <v>46206</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10411,7 +10416,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>10.5</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10454,7 +10459,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10468,10 +10473,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45103</v>
+        <v>44949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10484,7 +10489,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10527,7 +10532,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10541,10 +10546,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45256</v>
+        <v>45103</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10557,7 +10562,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10600,7 +10605,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10610,14 +10615,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46126</v>
+        <v>45229</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10630,7 +10635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10673,7 +10678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10683,14 +10688,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45642</v>
+        <v>45303</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10703,7 +10708,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10746,7 +10751,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10760,10 +10765,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45425</v>
+        <v>46253</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10775,13 +10780,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>13.9</v>
+        <v>6.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10838,10 +10838,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45553</v>
+        <v>45180</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>11.7</v>
+        <v>2.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10897,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45700</v>
+        <v>45355</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.4</v>
+        <v>27.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45405</v>
+        <v>46258</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11043,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11057,10 +11057,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45405</v>
+        <v>45103</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11116,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45229</v>
+        <v>46272</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45099</v>
+        <v>46272</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46009</v>
+        <v>46269</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11345,14 +11345,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45610</v>
+        <v>45700</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44928</v>
+        <v>45685</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.1</v>
+        <v>11.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45873</v>
+        <v>46275</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.9</v>
+        <v>2.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46146</v>
+        <v>44902</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46146</v>
+        <v>45553</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>11.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45776</v>
+        <v>44907</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44889</v>
+        <v>44928</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46154</v>
+        <v>44889</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45974</v>
+        <v>45776</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46155</v>
+        <v>45671</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12075,14 +12075,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45974</v>
+        <v>46286</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46009</v>
+        <v>45789</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45462</v>
+        <v>45789</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>11.1</v>
+        <v>5.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45974</v>
+        <v>46247</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>15.3</v>
+        <v>2.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 39266-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46200</v>
+        <v>46288</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46247</v>
+        <v>45796</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.3</v>
+        <v>10.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 39269-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46206</v>
+        <v>46288</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46253</v>
+        <v>45209</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46258</v>
+        <v>45579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46272</v>
+        <v>45068</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>8.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46272</v>
+        <v>45824</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.6</v>
+        <v>17.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46269</v>
+        <v>45835</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12938,27 +12938,27 @@
       </c>
       <c r="V167" s="2" t="inlineStr"/>
     </row>
-    <row r="168" ht="15" customHeight="1">
+    <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>S 1664-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46275</v>
+        <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13010,79 +13010,6 @@
         <v>0</v>
       </c>
       <c r="V168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>S 1664-2025</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D169" s="1" t="n">
-        <v>45803</v>
-      </c>
-      <c r="E169" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I169" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J169" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" t="n">
-        <v>0</v>
-      </c>
-      <c r="L169" t="n">
-        <v>0</v>
-      </c>
-      <c r="M169" t="n">
-        <v>0</v>
-      </c>
-      <c r="N169" t="n">
-        <v>0</v>
-      </c>
-      <c r="O169" t="n">
-        <v>0</v>
-      </c>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0</v>
-      </c>
-      <c r="S169" t="n">
-        <v>0</v>
-      </c>
-      <c r="T169" t="n">
-        <v>0</v>
-      </c>
-      <c r="U169" t="n">
-        <v>0</v>
-      </c>
-      <c r="V169" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -663,31 +663,31 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>45671</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 41136-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44884</v>
+        <v>45173</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45359</v>
+        <v>45716</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44579</v>
+        <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45685</v>
+        <v>45173</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45099</v>
+        <v>45405</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45716</v>
+        <v>44901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>12.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45261</v>
+        <v>45103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45076</v>
+        <v>46009</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.5</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45645</v>
+        <v>45796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>10.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45636</v>
+        <v>45209</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>18.6</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45636</v>
+        <v>45579</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45597</v>
+        <v>45894</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44629</v>
+        <v>44872</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.3</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45581</v>
+        <v>45636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45597</v>
+        <v>45590</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45597</v>
+        <v>45903</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44872</v>
+        <v>45903</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45369</v>
+        <v>45910</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>12.4</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45520</v>
+        <v>45639</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.7</v>
+        <v>10.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45103</v>
+        <v>45922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45645</v>
+        <v>45922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10.5</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45044</v>
+        <v>45922</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45894</v>
+        <v>46073</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45197</v>
+        <v>45068</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45903</v>
+        <v>45581</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45903</v>
+        <v>45936</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45716</v>
+        <v>45359</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45910</v>
+        <v>45943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4400,14 +4400,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45142</v>
+        <v>45945</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45581</v>
+        <v>45946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>8.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>45946</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45922</v>
+        <v>45180</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>45953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4765,14 +4765,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45610</v>
+        <v>45953</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45936</v>
+        <v>45581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45636</v>
+        <v>45968</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45943</v>
+        <v>45966</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45945</v>
+        <v>45973</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5130,14 +5130,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45078</v>
+        <v>46126</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45946</v>
+        <v>45973</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.5</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45946</v>
+        <v>44482</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45953</v>
+        <v>45645</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45229</v>
+        <v>45986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45953</v>
+        <v>44750</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5514,8 +5514,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5558,7 +5563,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5572,10 +5577,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45425</v>
+        <v>45987</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5587,13 +5592,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>13.9</v>
+        <v>4.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5636,7 +5636,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45181</v>
+        <v>45987</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5709,7 +5709,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45873</v>
+        <v>45989</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5782,7 +5782,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45966</v>
+        <v>46009</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>8.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45968</v>
+        <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45279</v>
+        <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45973</v>
+        <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45973</v>
+        <v>45873</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.9</v>
+        <v>6.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45405</v>
+        <v>46006</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45405</v>
+        <v>46007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45642</v>
+        <v>46007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44957</v>
+        <v>46007</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45987</v>
+        <v>46008</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45208</v>
+        <v>45217</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45987</v>
+        <v>46008</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45986</v>
+        <v>45685</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45989</v>
+        <v>45685</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>11.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46146</v>
+        <v>45824</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>17.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6960,14 +6960,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44908</v>
+        <v>45197</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45716</v>
+        <v>44629</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>13.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45716</v>
+        <v>45044</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7186,7 +7186,7 @@
         <v>46146</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44813</v>
+        <v>46146</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46155</v>
+        <v>44813</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46002</v>
+        <v>45597</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7478,7 +7478,7 @@
         <v>46154</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46002</v>
+        <v>45835</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46002</v>
+        <v>45974</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46002</v>
+        <v>46155</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>9</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46007</v>
+        <v>45278</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46006</v>
+        <v>45303</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46007</v>
+        <v>45369</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>10.2</v>
+        <v>12.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45974</v>
+        <v>44949</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46007</v>
+        <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46008</v>
+        <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45642</v>
+        <v>46009</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>11.7</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45642</v>
+        <v>45462</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44750</v>
+        <v>45974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8366,13 +8366,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>4.7</v>
+        <v>15.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8415,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8425,14 +8420,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46008</v>
+        <v>45142</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8445,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8488,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8502,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45603</v>
+        <v>45671</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8518,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8561,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8575,10 +8570,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46009</v>
+        <v>45603</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8591,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8634,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8644,14 +8639,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45278</v>
+        <v>44908</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8664,7 +8659,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8707,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8721,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44508</v>
+        <v>44957</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8737,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8780,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8794,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44482</v>
+        <v>45597</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8810,7 +8805,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8853,7 +8848,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8867,10 +8862,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45462</v>
+        <v>45415</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8883,7 +8878,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>11.1</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8926,7 +8921,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8940,10 +8935,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46009</v>
+        <v>45129</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8956,7 +8951,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8999,7 +8994,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9013,10 +9008,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45974</v>
+        <v>45355</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9029,7 +9024,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.6</v>
+        <v>27.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9072,7 +9067,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9086,10 +9081,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45974</v>
+        <v>45636</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9102,7 +9097,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>15.3</v>
+        <v>18.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9145,7 +9140,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9159,10 +9154,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45639</v>
+        <v>44579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9175,7 +9170,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>10.3</v>
+        <v>5.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9218,7 +9213,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9232,10 +9227,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45671</v>
+        <v>45636</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9248,7 +9243,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9291,7 +9286,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9305,10 +9300,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46073</v>
+        <v>46200</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9321,7 +9316,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9364,7 +9359,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9378,10 +9373,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44817</v>
+        <v>45103</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9394,7 +9389,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9437,7 +9432,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9451,10 +9446,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45256</v>
+        <v>45078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9467,7 +9462,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9510,7 +9505,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9524,10 +9519,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45173</v>
+        <v>46206</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9540,7 +9535,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9583,7 +9578,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9597,10 +9592,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45173</v>
+        <v>44586</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9613,7 +9608,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>7.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9656,7 +9651,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9670,10 +9665,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45405</v>
+        <v>45716</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9686,7 +9681,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9729,7 +9724,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9743,10 +9738,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44901</v>
+        <v>46253</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9759,7 +9754,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>12.1</v>
+        <v>6.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9802,7 +9797,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9816,10 +9811,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45415</v>
+        <v>46258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9832,7 +9827,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9875,7 +9870,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9885,14 +9880,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46126</v>
+        <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9905,7 +9900,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9948,7 +9943,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9962,10 +9957,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45191</v>
+        <v>45181</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9978,7 +9973,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>14.9</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10021,7 +10016,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10035,10 +10030,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45217</v>
+        <v>45229</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10051,7 +10046,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10094,7 +10089,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10108,10 +10103,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45129</v>
+        <v>45642</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10124,7 +10119,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>11.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10167,7 +10162,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10181,10 +10176,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45590</v>
+        <v>45642</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10197,7 +10192,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10240,7 +10235,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10254,10 +10249,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44586</v>
+        <v>45191</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10270,7 +10265,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>7.9</v>
+        <v>14.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10313,7 +10308,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10327,10 +10322,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46200</v>
+        <v>45208</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10386,7 +10381,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10400,10 +10395,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46206</v>
+        <v>44817</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10416,7 +10411,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10459,7 +10454,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10473,10 +10468,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44949</v>
+        <v>46272</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10489,7 +10484,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10532,7 +10527,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10546,10 +10541,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45103</v>
+        <v>46272</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10562,7 +10557,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10605,7 +10600,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10619,10 +10614,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45229</v>
+        <v>46269</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10635,7 +10630,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10678,7 +10673,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10688,14 +10683,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45303</v>
+        <v>45279</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10708,7 +10703,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10751,7 +10746,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10765,10 +10760,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10781,7 +10776,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10824,7 +10819,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10838,10 +10833,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45180</v>
+        <v>45716</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,7 +10849,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10897,7 +10892,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10906,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45355</v>
+        <v>45716</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10922,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>27.1</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10965,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10979,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46258</v>
+        <v>45671</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11000,7 +10995,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11043,7 +11038,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11053,14 +11048,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45103</v>
+        <v>46286</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11073,7 +11068,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11116,7 +11111,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11125,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46272</v>
+        <v>44907</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11141,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11184,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11198,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46272</v>
+        <v>45261</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11219,7 +11214,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11257,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11276,10 +11271,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46269</v>
+        <v>45520</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11292,7 +11287,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11330,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 39269-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11349,10 +11344,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45700</v>
+        <v>46288</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11360,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11403,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 39266-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11417,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45685</v>
+        <v>46288</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11433,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>11.1</v>
+        <v>2.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11476,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11490,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46275</v>
+        <v>44902</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11506,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11549,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11563,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44902</v>
+        <v>46247</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11579,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11622,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11636,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45553</v>
+        <v>45597</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11652,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>11.7</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11695,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11709,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44907</v>
+        <v>45076</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11725,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.9</v>
+        <v>10.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11768,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11782,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44928</v>
+        <v>45103</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11803,7 +11798,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11846,7 +11841,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11860,10 +11855,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44889</v>
+        <v>45256</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11871,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11914,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11928,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45776</v>
+        <v>45642</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11944,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11987,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12001,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45671</v>
+        <v>45425</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12021,8 +12016,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>13.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 38860-2026</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12075,14 +12075,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46286</v>
+        <v>45553</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>11.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45789</v>
+        <v>45700</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45789</v>
+        <v>45405</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46247</v>
+        <v>45405</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 39266-2026</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46288</v>
+        <v>45229</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45796</v>
+        <v>45099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>10.9</v>
+        <v>1.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 39269-2026</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12513,14 +12513,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46288</v>
+        <v>45610</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45209</v>
+        <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45579</v>
+        <v>45776</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45068</v>
+        <v>44889</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45824</v>
+        <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>17.8</v>
+        <v>5.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45835</v>
+        <v>45789</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44884</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45671</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45173</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45716</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45173</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>45405</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>46009</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45209</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>45579</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45894</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44872</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>45590</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>45903</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45903</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>45910</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>45639</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>45922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45922</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>46073</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45068</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45581</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45936</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45359</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45945</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45946</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>45180</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45953</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45968</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45966</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>45973</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>46126</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>45973</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44482</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45645</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>45986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44750</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45987</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>45987</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45989</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>46009</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>45873</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46006</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>46007</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>46008</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45217</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>46008</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45685</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45685</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45824</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45197</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44629</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45044</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>46146</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>46146</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44813</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45597</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>46154</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45835</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45974</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>46155</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45278</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>45303</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45369</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>44949</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>46009</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45462</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>45974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45142</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45671</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45603</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44908</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44957</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45597</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45415</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45129</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45355</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45636</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45636</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>46200</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45103</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>46206</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44586</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>45716</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46253</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>46258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45181</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>45229</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45642</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45642</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45191</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45208</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44817</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>46272</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>46272</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>46269</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45279</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>46275</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>45716</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>45716</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45671</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>46286</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>44907</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>45261</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>45520</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>46288</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>46288</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44902</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>46247</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>45597</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45076</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45103</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>45256</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>45642</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>45425</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45553</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45700</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45405</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45405</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>45229</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>45610</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45776</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44889</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45789</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -601,7 +601,7 @@
         <v>44884</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45671</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45173</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44465</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44886</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44883</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45716</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45173</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>45405</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>46009</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45209</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>45579</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45894</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44872</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>45590</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>45903</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45903</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>45910</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>45639</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>45922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45922</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>46073</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45068</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45581</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45936</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45359</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45945</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45946</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>45180</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45953</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45968</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45966</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>45973</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>46126</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>45973</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44482</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45645</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>45986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44750</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45987</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>45987</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45989</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>46009</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>45873</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46006</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>46007</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>46008</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45217</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>46008</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45685</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45685</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45824</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45197</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44629</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45044</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>46146</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>46146</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44813</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45597</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>46154</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45835</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45974</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>46155</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45278</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>45303</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45369</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>44949</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>46009</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45462</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>45974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45142</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45671</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45603</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44908</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44957</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45597</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45415</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45129</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45355</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45636</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45636</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>46200</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45103</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>46206</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44586</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>45716</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46253</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>46258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45181</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>45229</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45642</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45642</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45191</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45208</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44817</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>46272</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>46272</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>46269</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45279</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>46275</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>45716</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>45716</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45671</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>46286</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>44907</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>45261</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>45520</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>46288</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>46288</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44902</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>46247</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>45597</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45076</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45103</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>45256</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>45642</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>45425</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45553</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45700</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45405</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45405</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>45229</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>45610</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45776</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44889</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45789</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE168"/>
+  <dimension ref="A1:AE167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 1855-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44884</v>
+        <v>45671</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -647,12 +647,130 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Gammelgransskål
+Tretåig hackspett
+Ullticka
+Lappranunkel
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Z2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 41136-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
         <v>26</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>26</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -662,157 +780,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 1855-2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Gammelgransskål
-Tretåig hackspett
-Ullticka
-Lappranunkel
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 21714-2026</t>
+          <t>A 63800-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46149</v>
+        <v>45278</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1099,159 +1099,159 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 21714-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Rödvingetrast</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 63800-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45278</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Trana</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49284-2022</t>
+          <t>A 28542-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44861</v>
+        <v>44748</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28542-2022</t>
+          <t>A 49284-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44748</v>
+        <v>44861</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52391-2021</t>
+          <t>A 54997-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44465</v>
+        <v>44886</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>9.1</v>
+        <v>6.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54997-2022</t>
+          <t>A 54632-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44886</v>
+        <v>44883</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54632-2022</t>
+          <t>A 30003-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44883</v>
+        <v>44756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30003-2022</t>
+          <t>A 47661-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44756</v>
+        <v>44854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>9.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47661-2022</t>
+          <t>A 60754-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44854</v>
+        <v>44496</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>9.9</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60754-2021</t>
+          <t>A 71446-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44496</v>
+        <v>44540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 71446-2021</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44540</v>
+        <v>45359</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45716</v>
+        <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45173</v>
+        <v>45685</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45173</v>
+        <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45405</v>
+        <v>45261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44901</v>
+        <v>45716</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45103</v>
+        <v>46002</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45796</v>
+        <v>46002</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.9</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45209</v>
+        <v>45789</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45579</v>
+        <v>46002</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45894</v>
+        <v>46007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44872</v>
+        <v>46006</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45636</v>
+        <v>46007</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.8</v>
+        <v>10.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45590</v>
+        <v>46007</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45903</v>
+        <v>45076</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45903</v>
+        <v>46008</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45910</v>
+        <v>45645</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45639</v>
+        <v>45796</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45922</v>
+        <v>46008</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45922</v>
+        <v>45209</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45922</v>
+        <v>45579</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46073</v>
+        <v>45894</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45068</v>
+        <v>45903</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45581</v>
+        <v>45903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45936</v>
+        <v>45068</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>8.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45359</v>
+        <v>45636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>18.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45943</v>
+        <v>45636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45945</v>
+        <v>45597</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45946</v>
+        <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45946</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45180</v>
+        <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45953</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45953</v>
+        <v>45824</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.7</v>
+        <v>17.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45581</v>
+        <v>44629</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>13.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45968</v>
+        <v>45835</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45966</v>
+        <v>45936</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45973</v>
+        <v>45943</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5130,14 +5130,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46126</v>
+        <v>45945</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45973</v>
+        <v>45946</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>8.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44482</v>
+        <v>45946</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45645</v>
+        <v>46009</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10.5</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45986</v>
+        <v>45581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44750</v>
+        <v>45953</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5514,13 +5514,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5563,7 +5558,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5577,10 +5572,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45987</v>
+        <v>45597</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5593,7 +5588,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5636,7 +5631,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5650,10 +5645,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45987</v>
+        <v>45953</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5666,7 +5661,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5709,7 +5704,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5723,10 +5718,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45989</v>
+        <v>44872</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5739,7 +5734,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5782,7 +5777,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5796,10 +5791,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46009</v>
+        <v>45597</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5807,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.1</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5850,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46002</v>
+        <v>45966</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5880,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5923,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5942,10 +5937,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46002</v>
+        <v>45369</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5953,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9</v>
+        <v>12.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +5996,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46002</v>
+        <v>45968</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6026,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6069,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6088,10 +6083,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46002</v>
+        <v>45973</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6147,7 +6142,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6161,10 +6156,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45873</v>
+        <v>45973</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6177,7 +6172,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6215,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6229,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46006</v>
+        <v>45987</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6245,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6288,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6302,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46007</v>
+        <v>45987</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6318,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6361,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6375,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46007</v>
+        <v>45986</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6391,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6434,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6448,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46007</v>
+        <v>45520</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6464,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>10.2</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6507,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6521,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46008</v>
+        <v>45989</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6537,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6580,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6599,10 +6594,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45217</v>
+        <v>45103</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6610,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6653,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6667,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46008</v>
+        <v>45645</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6683,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.3</v>
+        <v>10.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6726,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6740,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45685</v>
+        <v>45044</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6756,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6799,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6813,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45685</v>
+        <v>45197</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6829,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>11.1</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6872,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6886,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45824</v>
+        <v>45639</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6902,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>17.8</v>
+        <v>10.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6945,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6964,10 +6959,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45197</v>
+        <v>45716</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6975,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7018,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7033,14 +7028,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44629</v>
+        <v>45142</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7048,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>13.3</v>
+        <v>4.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7091,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7110,10 +7105,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45044</v>
+        <v>46073</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7121,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7164,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7183,10 +7178,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46146</v>
+        <v>45581</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7194,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7237,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7252,14 +7247,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46146</v>
+        <v>45610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7267,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7310,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7329,10 +7324,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44813</v>
+        <v>45636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7340,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7383,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7397,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45597</v>
+        <v>45078</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7413,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7456,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7475,10 +7470,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46154</v>
+        <v>45229</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7491,7 +7486,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7534,7 +7529,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7548,10 +7543,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45835</v>
+        <v>45425</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7563,8 +7558,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>13.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45974</v>
+        <v>45181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46155</v>
+        <v>45279</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7763,14 +7763,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45278</v>
+        <v>46126</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45303</v>
+        <v>45405</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45369</v>
+        <v>45405</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>12.4</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44949</v>
+        <v>45642</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44508</v>
+        <v>44957</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45974</v>
+        <v>45208</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8201,14 +8201,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46009</v>
+        <v>44908</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45462</v>
+        <v>45716</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>11.1</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45974</v>
+        <v>45716</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>15.3</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8420,14 +8420,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45142</v>
+        <v>44813</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45671</v>
+        <v>45642</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.1</v>
+        <v>11.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45603</v>
+        <v>45642</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44908</v>
+        <v>44750</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8658,8 +8658,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8707,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8721,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44957</v>
+        <v>45603</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8737,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8780,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8794,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45597</v>
+        <v>45873</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8805,7 +8810,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8848,7 +8853,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8862,10 +8867,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45415</v>
+        <v>45278</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8878,7 +8883,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8921,7 +8926,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8935,10 +8940,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45129</v>
+        <v>46009</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8951,7 +8956,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>8.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8994,7 +8999,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9008,10 +9013,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45355</v>
+        <v>44508</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9024,7 +9029,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>27.1</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9067,7 +9072,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9081,10 +9086,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45636</v>
+        <v>44482</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9097,7 +9102,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>18.6</v>
+        <v>5.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9140,7 +9145,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9154,10 +9159,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44579</v>
+        <v>46146</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9170,7 +9175,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9213,7 +9218,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9227,10 +9232,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45636</v>
+        <v>46146</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9243,7 +9248,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9286,7 +9291,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9300,10 +9305,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46200</v>
+        <v>46155</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9316,7 +9321,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9359,7 +9364,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9373,10 +9378,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45103</v>
+        <v>45671</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9389,7 +9394,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9432,7 +9437,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9446,10 +9451,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45078</v>
+        <v>46154</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9462,7 +9467,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9505,7 +9510,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9519,10 +9524,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46206</v>
+        <v>45974</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9535,7 +9540,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9578,7 +9583,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9592,10 +9597,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44586</v>
+        <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9608,7 +9613,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>7.9</v>
+        <v>3.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9651,7 +9656,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9665,10 +9670,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45716</v>
+        <v>45256</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9681,7 +9686,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9724,7 +9729,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9738,10 +9743,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46253</v>
+        <v>45462</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9754,7 +9759,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6.4</v>
+        <v>11.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9797,7 +9802,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9811,10 +9816,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46258</v>
+        <v>46009</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9827,7 +9832,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9870,7 +9875,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9884,10 +9889,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45645</v>
+        <v>45974</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9900,7 +9905,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9943,7 +9948,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9957,10 +9962,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45181</v>
+        <v>45974</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9973,7 +9978,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>15.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10016,7 +10021,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10030,10 +10035,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45229</v>
+        <v>45173</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10046,7 +10051,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10089,7 +10094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10103,10 +10108,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45642</v>
+        <v>45173</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10119,7 +10124,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>11.7</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10162,7 +10167,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10176,10 +10181,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45642</v>
+        <v>45405</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10192,7 +10197,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10235,7 +10240,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10249,10 +10254,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45191</v>
+        <v>44901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10265,7 +10270,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>14.9</v>
+        <v>12.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10308,7 +10313,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10322,10 +10327,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45208</v>
+        <v>45415</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10338,7 +10343,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10381,7 +10386,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10395,10 +10400,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44817</v>
+        <v>45191</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10411,7 +10416,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.9</v>
+        <v>14.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10454,7 +10459,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10468,10 +10473,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46272</v>
+        <v>45217</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10484,7 +10489,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10527,7 +10532,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10541,10 +10546,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46272</v>
+        <v>45129</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10557,7 +10562,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10600,7 +10605,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10614,10 +10619,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46269</v>
+        <v>45590</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10630,7 +10635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10673,7 +10678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10687,10 +10692,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45279</v>
+        <v>44586</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10703,7 +10708,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.2</v>
+        <v>7.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10746,7 +10751,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10760,10 +10765,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46275</v>
+        <v>44949</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10776,7 +10781,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10819,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10833,10 +10838,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45716</v>
+        <v>45103</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10849,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10892,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10906,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45716</v>
+        <v>46200</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10922,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10965,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10979,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45671</v>
+        <v>45229</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -10995,7 +11000,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11038,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 38860-2026</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11052,10 +11057,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46286</v>
+        <v>45303</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11068,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11111,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11125,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44907</v>
+        <v>46206</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11141,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11184,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11198,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45261</v>
+        <v>45180</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11214,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11257,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11271,10 +11276,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45520</v>
+        <v>46253</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11287,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11330,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39269-2026</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11344,10 +11349,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46288</v>
+        <v>45355</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11360,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>27.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11403,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 39266-2026</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11417,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46288</v>
+        <v>46258</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11433,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11476,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11490,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44902</v>
+        <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11506,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11549,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11563,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46247</v>
+        <v>45700</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11579,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11622,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11636,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45597</v>
+        <v>45685</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11652,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>11.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11695,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11709,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45076</v>
+        <v>46272</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11725,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11768,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11782,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45103</v>
+        <v>46272</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11798,7 +11803,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11841,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11855,10 +11860,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45256</v>
+        <v>46269</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11871,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11914,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11928,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45642</v>
+        <v>44902</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11944,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11987,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12001,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45425</v>
+        <v>45553</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12016,13 +12021,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>13.9</v>
+        <v>11.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45553</v>
+        <v>46275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>11.7</v>
+        <v>2.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45700</v>
+        <v>44907</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45405</v>
+        <v>44928</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45405</v>
+        <v>44889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.7</v>
+        <v>7.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45229</v>
+        <v>45776</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>8.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45099</v>
+        <v>45789</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12513,14 +12513,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45610</v>
+        <v>45671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12586,14 +12586,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44928</v>
+        <v>46286</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 39266-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45776</v>
+        <v>46288</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 39269-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44889</v>
+        <v>46288</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45789</v>
+        <v>46247</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12865,27 +12865,27 @@
       </c>
       <c r="V166" s="2" t="inlineStr"/>
     </row>
-    <row r="167" ht="15" customHeight="1">
+    <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>S 1664-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45789</v>
+        <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12937,79 +12937,6 @@
         <v>0</v>
       </c>
       <c r="V167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>S 1664-2025</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D168" s="1" t="n">
-        <v>45803</v>
-      </c>
-      <c r="E168" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I168" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" t="n">
-        <v>0</v>
-      </c>
-      <c r="M168" t="n">
-        <v>0</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0</v>
-      </c>
-      <c r="O168" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
-      </c>
-      <c r="S168" t="n">
-        <v>0</v>
-      </c>
-      <c r="T168" t="n">
-        <v>0</v>
-      </c>
-      <c r="U168" t="n">
-        <v>0</v>
-      </c>
-      <c r="V168" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 1855-2025</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45671</v>
+        <v>44884</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -647,12 +647,122 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
+        <v>26</v>
+      </c>
+      <c r="U2" t="n">
+        <v>26</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gammelgransskål
+Vedskivlav
+Nästlav
+Vedticka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 1855-2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45671</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gammelgransskål
@@ -662,115 +772,115 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 41136-2023</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>45173</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E4" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>5.7</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S4" t="n">
         <v>6</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>26</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>26</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -780,145 +890,35 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 54858-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44884</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>26</v>
-      </c>
-      <c r="U4" t="n">
-        <v>26</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gammelgransskål
-Vedskivlav
-Nästlav
-Vedticka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45278</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>46149</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44748</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44861</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44886</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44883</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44496</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45359</v>
+        <v>45716</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44579</v>
+        <v>45173</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45685</v>
+        <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45099</v>
+        <v>45405</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45261</v>
+        <v>44901</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>9.199999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45716</v>
+        <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46002</v>
+        <v>45796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>10.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46002</v>
+        <v>45209</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45789</v>
+        <v>45579</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46002</v>
+        <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46007</v>
+        <v>44872</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46006</v>
+        <v>45903</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46007</v>
+        <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46007</v>
+        <v>45068</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45076</v>
+        <v>45636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46008</v>
+        <v>45590</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45645</v>
+        <v>45910</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45796</v>
+        <v>45824</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10.9</v>
+        <v>17.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46008</v>
+        <v>45922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45209</v>
+        <v>45922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45579</v>
+        <v>45922</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45894</v>
+        <v>45835</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45903</v>
+        <v>45581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45903</v>
+        <v>45936</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45068</v>
+        <v>45359</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.6</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45636</v>
+        <v>45943</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>18.6</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45636</v>
+        <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45597</v>
+        <v>45946</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45910</v>
+        <v>45946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>45180</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45922</v>
+        <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>45953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45824</v>
+        <v>45639</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>17.8</v>
+        <v>10.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44629</v>
+        <v>45968</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>13.3</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45835</v>
+        <v>45966</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45936</v>
+        <v>45581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45943</v>
+        <v>45973</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45945</v>
+        <v>45973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.7</v>
+        <v>4.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45946</v>
+        <v>44482</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.5</v>
+        <v>5.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45946</v>
+        <v>45645</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46009</v>
+        <v>46073</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45581</v>
+        <v>45986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45953</v>
+        <v>44750</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5514,8 +5514,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5558,7 +5563,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5572,10 +5577,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45597</v>
+        <v>45987</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5588,7 +5593,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5631,7 +5636,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5645,10 +5650,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45953</v>
+        <v>45987</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5661,7 +5666,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5704,7 +5709,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5718,10 +5723,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44872</v>
+        <v>45989</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5734,7 +5739,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5777,7 +5782,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5791,10 +5796,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45597</v>
+        <v>46002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5807,7 +5812,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5850,7 +5855,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5864,10 +5869,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45966</v>
+        <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5880,7 +5885,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5923,7 +5928,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5937,10 +5942,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45369</v>
+        <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5953,7 +5958,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>12.4</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5996,7 +6001,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45968</v>
+        <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6026,7 +6031,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6069,7 +6074,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6083,10 +6088,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45973</v>
+        <v>46006</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6099,7 +6104,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6142,7 +6147,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6156,10 +6161,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45973</v>
+        <v>46007</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6172,7 +6177,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6215,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6229,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45987</v>
+        <v>46007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6245,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6288,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6302,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45987</v>
+        <v>46007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6318,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.9</v>
+        <v>10.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6361,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6375,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45986</v>
+        <v>46008</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6391,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6434,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6448,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45520</v>
+        <v>46008</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6464,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6507,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6521,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45989</v>
+        <v>45217</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6537,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6580,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6594,10 +6599,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45103</v>
+        <v>45685</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6610,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45645</v>
+        <v>45685</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6683,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6740,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45044</v>
+        <v>45197</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6756,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6799,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6813,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45197</v>
+        <v>44629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6829,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>13.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6872,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6886,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45639</v>
+        <v>45044</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6902,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>10.3</v>
+        <v>5.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6945,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6959,10 +6964,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45716</v>
+        <v>44813</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6975,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7018,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7032,10 +7037,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45142</v>
+        <v>46126</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7048,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7091,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7105,10 +7110,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46073</v>
+        <v>45597</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7121,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7164,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7178,10 +7183,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45581</v>
+        <v>45278</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7194,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7237,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7251,10 +7256,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45610</v>
+        <v>45303</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7267,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7310,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7324,10 +7329,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45636</v>
+        <v>45369</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7340,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.8</v>
+        <v>12.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7383,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7397,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45078</v>
+        <v>44949</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7413,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7456,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7470,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45229</v>
+        <v>44508</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7486,7 +7491,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7529,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7539,14 +7544,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45425</v>
+        <v>45142</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7558,13 +7563,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>13.9</v>
+        <v>4.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45181</v>
+        <v>45671</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45279</v>
+        <v>46009</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.2</v>
+        <v>8.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7763,14 +7763,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46126</v>
+        <v>45603</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45405</v>
+        <v>44908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45405</v>
+        <v>45873</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45642</v>
+        <v>44957</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44957</v>
+        <v>45597</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45208</v>
+        <v>45415</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8201,14 +8201,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44908</v>
+        <v>45129</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45716</v>
+        <v>45355</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>27.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45716</v>
+        <v>45636</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>18.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44813</v>
+        <v>44579</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45642</v>
+        <v>46146</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>11.7</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45642</v>
+        <v>46146</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44750</v>
+        <v>45636</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8658,13 +8658,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8707,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8721,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45603</v>
+        <v>45103</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8737,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8780,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8794,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45873</v>
+        <v>45078</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8810,7 +8805,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6.9</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8853,7 +8848,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8867,10 +8862,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45278</v>
+        <v>46154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8883,7 +8878,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8926,7 +8921,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8940,10 +8935,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46009</v>
+        <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8956,7 +8951,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8999,7 +8994,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9013,10 +9008,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44508</v>
+        <v>46155</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9029,7 +9024,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9072,7 +9067,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9086,10 +9081,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44482</v>
+        <v>44586</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9102,7 +9097,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.4</v>
+        <v>7.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9145,7 +9140,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9159,10 +9154,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46146</v>
+        <v>45716</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9175,7 +9170,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9218,7 +9213,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9232,10 +9227,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46146</v>
+        <v>45974</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9248,7 +9243,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9291,7 +9286,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9305,10 +9300,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46155</v>
+        <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9321,7 +9316,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9364,7 +9359,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9378,10 +9373,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45671</v>
+        <v>45462</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9394,7 +9389,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>11.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9437,7 +9432,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9451,10 +9446,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46154</v>
+        <v>45974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9467,7 +9462,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.8</v>
+        <v>15.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9510,7 +9505,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9524,10 +9519,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45974</v>
+        <v>45645</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9540,7 +9535,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9583,7 +9578,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9597,10 +9592,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44817</v>
+        <v>45181</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9613,7 +9608,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9656,7 +9651,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9670,10 +9665,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45256</v>
+        <v>45229</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9686,7 +9681,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9729,7 +9724,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9743,10 +9738,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45462</v>
+        <v>45642</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9759,7 +9754,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9802,7 +9797,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9816,10 +9811,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46009</v>
+        <v>45642</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9832,7 +9827,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9875,7 +9870,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9889,10 +9884,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45974</v>
+        <v>45191</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9905,7 +9900,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.6</v>
+        <v>14.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9948,7 +9943,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9962,10 +9957,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45974</v>
+        <v>45208</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9978,7 +9973,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>15.3</v>
+        <v>3.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10021,7 +10016,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10035,10 +10030,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45173</v>
+        <v>44817</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10051,7 +10046,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10094,7 +10089,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10108,10 +10103,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45173</v>
+        <v>45279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10124,7 +10119,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10167,7 +10162,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10181,10 +10176,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45405</v>
+        <v>45716</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10197,7 +10192,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10240,7 +10235,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10254,10 +10249,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44901</v>
+        <v>45716</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10270,7 +10265,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>12.1</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10313,7 +10308,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10327,10 +10322,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45415</v>
+        <v>46200</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10386,7 +10381,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10400,10 +10395,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45191</v>
+        <v>44907</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10416,7 +10411,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>14.9</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10459,7 +10454,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10473,10 +10468,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45217</v>
+        <v>45261</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10489,7 +10484,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10532,7 +10527,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10546,10 +10541,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45129</v>
+        <v>45520</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10562,7 +10557,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10605,7 +10600,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10619,10 +10614,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45590</v>
+        <v>46206</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10635,7 +10630,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10678,7 +10673,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10692,10 +10687,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44586</v>
+        <v>46253</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10708,7 +10703,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10751,7 +10746,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10765,10 +10760,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44949</v>
+        <v>44902</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10781,7 +10776,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10824,7 +10819,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10838,10 +10833,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45103</v>
+        <v>45597</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,7 +10849,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10897,7 +10892,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10906,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46200</v>
+        <v>46258</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10922,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10965,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10979,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45229</v>
+        <v>45076</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11000,7 +10995,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>10.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11043,7 +11038,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11053,14 +11048,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45303</v>
+        <v>45103</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11073,7 +11068,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11116,7 +11111,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11125,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46206</v>
+        <v>45256</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11141,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11184,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11198,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45180</v>
+        <v>45642</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11219,7 +11214,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11257,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11276,10 +11271,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46253</v>
+        <v>45425</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11291,8 +11286,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>6.4</v>
+        <v>13.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11349,10 +11349,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45355</v>
+        <v>45553</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>27.1</v>
+        <v>11.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46258</v>
+        <v>45700</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45103</v>
+        <v>46272</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45700</v>
+        <v>45405</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45685</v>
+        <v>45405</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>11.1</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46272</v>
+        <v>45229</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11790,7 +11790,7 @@
         <v>46272</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>46269</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44902</v>
+        <v>45099</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45553</v>
+        <v>46275</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>11.7</v>
+        <v>2.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12075,14 +12075,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46275</v>
+        <v>45610</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44907</v>
+        <v>44928</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44928</v>
+        <v>45671</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12294,14 +12294,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44889</v>
+        <v>46286</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 39269-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45776</v>
+        <v>46288</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 39266-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45789</v>
+        <v>46288</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45671</v>
+        <v>45776</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 38860-2026</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12586,14 +12586,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46286</v>
+        <v>44889</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 39266-2026</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46288</v>
+        <v>46247</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 39269-2026</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46288</v>
+        <v>45789</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46247</v>
+        <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
         <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 41136-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44884</v>
+        <v>45173</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -663,106 +663,216 @@
         </is>
       </c>
       <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 54858-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44884</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>26</v>
+      </c>
+      <c r="U3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gammelgransskål
+Vedskivlav
+Nästlav
+Vedticka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 1855-2025</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>45671</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E4" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>4.2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>4</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S4" t="n">
         <v>6</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>7</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gammelgransskål
@@ -772,153 +882,43 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="Z4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 41136-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45173</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>26</v>
-      </c>
-      <c r="U4" t="n">
-        <v>26</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gammelgransskål
-Vedskivlav
-Nästlav
-Vedticka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45278</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>46149</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28542-2022</t>
+          <t>A 49284-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44748</v>
+        <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49284-2022</t>
+          <t>A 28542-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44861</v>
+        <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1052-2022</t>
+          <t>A 64085-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44571</v>
+        <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 64085-2021</t>
+          <t>A 64088-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 64088-2021</t>
+          <t>A 49245-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44509</v>
+        <v>44861</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49245-2022</t>
+          <t>A 1052-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44861</v>
+        <v>44571</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54997-2022</t>
+          <t>A 60754-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44886</v>
+        <v>44496</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54632-2022</t>
+          <t>A 47661-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44883</v>
+        <v>44854</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>9.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30003-2022</t>
+          <t>A 54997-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44756</v>
+        <v>44886</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 47661-2022</t>
+          <t>A 71446-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44854</v>
+        <v>44540</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>9.9</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60754-2021</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44496</v>
+        <v>45359</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 71446-2021</t>
+          <t>A 54632-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44540</v>
+        <v>44883</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 30003-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45716</v>
+        <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45173</v>
+        <v>44872</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45173</v>
+        <v>44482</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45405</v>
+        <v>45597</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44901</v>
+        <v>45369</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2728,7 +2728,7 @@
         <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46009</v>
+        <v>44579</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45796</v>
+        <v>45685</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.9</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45209</v>
+        <v>45099</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45579</v>
+        <v>45671</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45894</v>
+        <v>45520</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44872</v>
+        <v>45700</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45903</v>
+        <v>45103</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45903</v>
+        <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>10.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45068</v>
+        <v>45685</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.6</v>
+        <v>11.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45636</v>
+        <v>45044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45590</v>
+        <v>45197</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45910</v>
+        <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45824</v>
+        <v>44817</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>17.8</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45922</v>
+        <v>45256</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45922</v>
+        <v>45261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45922</v>
+        <v>44902</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45835</v>
+        <v>45553</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>11.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45581</v>
+        <v>45716</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45936</v>
+        <v>45173</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45359</v>
+        <v>45173</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45943</v>
+        <v>44907</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45945</v>
+        <v>45405</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.7</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4400,14 +4400,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45946</v>
+        <v>45142</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45946</v>
+        <v>44901</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>12.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45180</v>
+        <v>45581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4619,14 +4619,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45953</v>
+        <v>45610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45953</v>
+        <v>44928</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45639</v>
+        <v>45415</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>10.3</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45968</v>
+        <v>44889</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45966</v>
+        <v>45776</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45581</v>
+        <v>45191</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>14.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45973</v>
+        <v>45636</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45973</v>
+        <v>45078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44482</v>
+        <v>45789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45645</v>
+        <v>45217</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46073</v>
+        <v>45129</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45986</v>
+        <v>45590</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44750</v>
+        <v>45789</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5514,13 +5514,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5563,7 +5558,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5577,10 +5572,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45987</v>
+        <v>45229</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5593,7 +5588,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5636,7 +5631,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5650,10 +5645,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45987</v>
+        <v>44586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5666,7 +5661,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.3</v>
+        <v>7.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5709,7 +5704,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5723,10 +5718,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45989</v>
+        <v>45425</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5738,8 +5733,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>13.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5782,7 +5782,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46002</v>
+        <v>45181</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46002</v>
+        <v>45076</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46002</v>
+        <v>45645</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46002</v>
+        <v>45796</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>10.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46006</v>
+        <v>45209</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46007</v>
+        <v>45579</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46007</v>
+        <v>45279</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46007</v>
+        <v>45636</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>10.2</v>
+        <v>18.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46008</v>
+        <v>45636</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46008</v>
+        <v>44949</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>7.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45217</v>
+        <v>45597</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45685</v>
+        <v>45103</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45685</v>
+        <v>45405</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>11.1</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45197</v>
+        <v>45405</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44629</v>
+        <v>45642</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>13.3</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45044</v>
+        <v>44957</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44813</v>
+        <v>45068</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7033,14 +7033,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46126</v>
+        <v>45229</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7106,14 +7106,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45597</v>
+        <v>45303</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45278</v>
+        <v>45208</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7252,14 +7252,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45303</v>
+        <v>44629</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>13.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7325,14 +7325,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45369</v>
+        <v>44908</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>12.4</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44949</v>
+        <v>45716</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44508</v>
+        <v>45716</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7534,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7544,14 +7544,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45142</v>
+        <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45671</v>
+        <v>44813</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46009</v>
+        <v>45824</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>8.1</v>
+        <v>17.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45603</v>
+        <v>45355</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.8</v>
+        <v>27.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44908</v>
+        <v>45835</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45873</v>
+        <v>45642</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6.9</v>
+        <v>11.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44957</v>
+        <v>45642</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45597</v>
+        <v>44750</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8074,8 +8074,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8123,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8137,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45415</v>
+        <v>45603</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8153,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8196,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8210,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45129</v>
+        <v>45278</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8226,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8269,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8283,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45355</v>
+        <v>44508</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8299,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>27.1</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8342,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8356,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45636</v>
+        <v>45581</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8372,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>18.6</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8415,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8429,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44579</v>
+        <v>45597</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8445,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8488,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8497,10 +8502,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46146</v>
+        <v>45936</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8518,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8561,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8575,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46146</v>
+        <v>45943</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8591,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8634,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8648,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45636</v>
+        <v>45945</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8659,7 +8664,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8707,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8721,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45103</v>
+        <v>45946</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8737,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>8.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8780,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8794,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45078</v>
+        <v>45946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8805,7 +8810,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8848,7 +8853,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8862,10 +8867,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46154</v>
+        <v>45894</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8878,7 +8883,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8921,7 +8926,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8935,10 +8940,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45974</v>
+        <v>45953</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8951,7 +8956,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8994,7 +8999,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9008,10 +9013,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46155</v>
+        <v>45953</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9024,7 +9029,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9067,7 +9072,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9081,10 +9086,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44586</v>
+        <v>45903</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9097,7 +9102,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>7.9</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9140,7 +9145,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9154,10 +9159,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45716</v>
+        <v>45903</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9170,7 +9175,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9213,7 +9218,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9227,10 +9232,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45974</v>
+        <v>45910</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9243,7 +9248,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9286,7 +9291,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9300,10 +9305,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46009</v>
+        <v>45966</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9316,7 +9321,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9359,7 +9364,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9373,10 +9378,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45462</v>
+        <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9389,7 +9394,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>11.1</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9432,7 +9437,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9446,10 +9451,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45974</v>
+        <v>45922</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9462,7 +9467,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>15.3</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9505,7 +9510,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9519,10 +9524,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45645</v>
+        <v>45968</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9535,7 +9540,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9578,7 +9583,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9592,10 +9597,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45181</v>
+        <v>45922</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9608,7 +9613,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9651,7 +9656,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9665,10 +9670,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45229</v>
+        <v>45973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9681,7 +9686,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9724,7 +9729,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9738,10 +9743,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45642</v>
+        <v>45973</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9754,7 +9759,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>11.7</v>
+        <v>4.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9797,7 +9802,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9811,10 +9816,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45642</v>
+        <v>45987</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9827,7 +9832,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9870,7 +9875,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9884,10 +9889,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45191</v>
+        <v>45987</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9900,7 +9905,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9943,7 +9948,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9957,10 +9962,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45208</v>
+        <v>45986</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9973,7 +9978,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10016,7 +10021,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10030,10 +10035,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44817</v>
+        <v>45989</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10046,7 +10051,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10089,7 +10094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10103,10 +10108,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45279</v>
+        <v>46002</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10119,7 +10124,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10162,7 +10167,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10176,10 +10181,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45716</v>
+        <v>46002</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10235,7 +10240,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10249,10 +10254,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45716</v>
+        <v>46002</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10265,7 +10270,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10308,7 +10313,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10322,10 +10327,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46200</v>
+        <v>46002</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10338,7 +10343,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10381,7 +10386,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10395,10 +10400,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44907</v>
+        <v>46007</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10411,7 +10416,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10454,7 +10459,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10468,10 +10473,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45261</v>
+        <v>46006</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10484,7 +10489,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10527,7 +10532,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10541,10 +10546,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45520</v>
+        <v>46007</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10557,7 +10562,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>10.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10600,7 +10605,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10614,10 +10619,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46206</v>
+        <v>46007</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10630,7 +10635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10673,7 +10678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10687,10 +10692,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46253</v>
+        <v>46008</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10703,7 +10708,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10746,7 +10751,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10760,10 +10765,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44902</v>
+        <v>46008</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10776,7 +10781,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10819,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10833,10 +10838,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45597</v>
+        <v>46009</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10849,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10892,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10906,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46258</v>
+        <v>45639</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10922,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.1</v>
+        <v>10.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10965,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10979,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45076</v>
+        <v>46073</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -10995,7 +11000,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11038,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11048,14 +11053,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45103</v>
+        <v>46126</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11068,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11111,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11125,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45256</v>
+        <v>45873</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11141,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>6.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11184,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11198,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45642</v>
+        <v>46009</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11214,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>8.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11257,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11271,10 +11276,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45425</v>
+        <v>46146</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11286,13 +11291,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>13.9</v>
+        <v>0.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11349,10 +11349,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45553</v>
+        <v>46146</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>11.7</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45700</v>
+        <v>46155</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46272</v>
+        <v>46154</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45405</v>
+        <v>45974</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45405</v>
+        <v>45462</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>11.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45229</v>
+        <v>46009</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46272</v>
+        <v>45974</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46269</v>
+        <v>45974</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>15.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45099</v>
+        <v>46200</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46275</v>
+        <v>46206</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12075,14 +12075,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45610</v>
+        <v>46258</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44928</v>
+        <v>46272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45671</v>
+        <v>46272</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 38860-2026</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12294,14 +12294,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46286</v>
+        <v>46269</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 39269-2026</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46288</v>
+        <v>46275</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39266-2026</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46288</v>
+        <v>45671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12513,14 +12513,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45776</v>
+        <v>46286</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 39266-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44889</v>
+        <v>46288</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 39269-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46247</v>
+        <v>46288</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45789</v>
+        <v>46247</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45789</v>
+        <v>46253</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
         <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -663,38 +663,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 1855-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44884</v>
+        <v>45671</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -757,12 +757,130 @@
         <v>6</v>
       </c>
       <c r="T3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Gammelgransskål
+Tretåig hackspett
+Ullticka
+Lappranunkel
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Z3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 41136-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="n">
         <v>26</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>26</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -772,150 +890,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 1855-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>7</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Gammelgransskål
-Tretåig hackspett
-Ullticka
-Lappranunkel
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 63800-2023</t>
+          <t>A 21714-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45278</v>
+        <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1099,155 +1099,155 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 63800-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Trana</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 21714-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 64085-2021</t>
+          <t>A 1052-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44509</v>
+        <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 64088-2021</t>
+          <t>A 64085-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 49245-2022</t>
+          <t>A 64088-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44861</v>
+        <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1052-2022</t>
+          <t>A 49245-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44571</v>
+        <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60754-2021</t>
+          <t>A 54997-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44496</v>
+        <v>44886</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 47661-2022</t>
+          <t>A 54632-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44854</v>
+        <v>44883</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>9.9</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54997-2022</t>
+          <t>A 30003-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44886</v>
+        <v>44756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 71446-2021</t>
+          <t>A 47661-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44540</v>
+        <v>44854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>9.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 60754-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45359</v>
+        <v>44496</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54632-2022</t>
+          <t>A 71446-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44883</v>
+        <v>44540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30003-2022</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44756</v>
+        <v>45716</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44872</v>
+        <v>45173</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44482</v>
+        <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45597</v>
+        <v>45405</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45369</v>
+        <v>44901</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2728,7 +2728,7 @@
         <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44579</v>
+        <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.8</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45685</v>
+        <v>45796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>10.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45099</v>
+        <v>45894</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45671</v>
+        <v>45903</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45520</v>
+        <v>45903</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45700</v>
+        <v>44872</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45103</v>
+        <v>45639</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>10.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45645</v>
+        <v>45209</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45685</v>
+        <v>45579</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>11.1</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45044</v>
+        <v>45910</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45197</v>
+        <v>45636</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45716</v>
+        <v>45590</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44817</v>
+        <v>45922</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45256</v>
+        <v>45922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45261</v>
+        <v>45922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>9.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44902</v>
+        <v>46073</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45553</v>
+        <v>45936</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>11.7</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45716</v>
+        <v>45068</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45173</v>
+        <v>45943</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45173</v>
+        <v>45945</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44907</v>
+        <v>45946</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>8.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45405</v>
+        <v>45946</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4400,14 +4400,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45142</v>
+        <v>45581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44901</v>
+        <v>45359</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>12.1</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45581</v>
+        <v>45953</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4619,14 +4619,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45610</v>
+        <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44928</v>
+        <v>45180</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45415</v>
+        <v>45968</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44889</v>
+        <v>45966</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45776</v>
+        <v>45973</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.4</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45191</v>
+        <v>45973</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5057,14 +5057,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45636</v>
+        <v>46126</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45078</v>
+        <v>45581</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45789</v>
+        <v>45986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45217</v>
+        <v>44482</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45129</v>
+        <v>45645</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>10.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45590</v>
+        <v>45987</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45789</v>
+        <v>45987</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5558,7 +5558,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45229</v>
+        <v>45989</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44586</v>
+        <v>46009</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5704,7 +5704,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45425</v>
+        <v>44750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>13.9</v>
+        <v>4.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5782,7 +5782,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45181</v>
+        <v>45824</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>17.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45076</v>
+        <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>10.5</v>
+        <v>2.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45645</v>
+        <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45796</v>
+        <v>45873</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45209</v>
+        <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45579</v>
+        <v>46002</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45279</v>
+        <v>46006</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45636</v>
+        <v>46007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>18.6</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45636</v>
+        <v>46007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44949</v>
+        <v>46007</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45597</v>
+        <v>46008</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45103</v>
+        <v>46008</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45405</v>
+        <v>45835</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45405</v>
+        <v>45217</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45642</v>
+        <v>45685</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44957</v>
+        <v>45685</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>11.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45068</v>
+        <v>45197</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45229</v>
+        <v>44629</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>13.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7106,14 +7106,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45303</v>
+        <v>45044</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45208</v>
+        <v>44813</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44629</v>
+        <v>46146</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>13.3</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7325,14 +7325,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44908</v>
+        <v>46146</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45716</v>
+        <v>45597</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45716</v>
+        <v>45278</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45180</v>
+        <v>46154</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7617,14 +7617,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44813</v>
+        <v>45303</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45824</v>
+        <v>45369</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17.8</v>
+        <v>12.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45355</v>
+        <v>45974</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>27.1</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45835</v>
+        <v>46155</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45642</v>
+        <v>44949</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>11.7</v>
+        <v>7.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45642</v>
+        <v>44508</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8055,14 +8055,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44750</v>
+        <v>45142</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8074,13 +8074,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8123,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8137,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45603</v>
+        <v>45671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8153,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8196,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8210,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45278</v>
+        <v>45974</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8226,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8269,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8283,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44508</v>
+        <v>46009</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8299,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8342,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8356,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45581</v>
+        <v>45462</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8372,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>11.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8415,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8429,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45597</v>
+        <v>45603</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8445,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8488,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8502,10 +8497,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45936</v>
+        <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8518,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>15.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8561,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8571,14 +8566,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45943</v>
+        <v>44908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8591,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8634,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8648,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45945</v>
+        <v>44957</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8664,7 +8659,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8707,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8721,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45946</v>
+        <v>45597</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8737,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8780,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8794,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45946</v>
+        <v>45415</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8810,7 +8805,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8853,7 +8848,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8867,10 +8862,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45894</v>
+        <v>45129</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8883,7 +8878,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8926,7 +8921,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8940,10 +8935,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45953</v>
+        <v>45355</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8956,7 +8951,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.7</v>
+        <v>27.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8999,7 +8994,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9013,10 +9008,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45953</v>
+        <v>45636</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9029,7 +9024,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.6</v>
+        <v>18.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9072,7 +9067,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9086,10 +9081,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45903</v>
+        <v>44579</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9102,7 +9097,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9145,7 +9140,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9159,10 +9154,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45903</v>
+        <v>45636</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9175,7 +9170,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9218,7 +9213,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9232,10 +9227,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45910</v>
+        <v>45103</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9248,7 +9243,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9291,7 +9286,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9305,10 +9300,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45966</v>
+        <v>45078</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9321,7 +9316,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9364,7 +9359,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9378,10 +9373,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45922</v>
+        <v>44586</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9394,7 +9389,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>7.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9437,7 +9432,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9451,10 +9446,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45922</v>
+        <v>45716</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9467,7 +9462,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9510,7 +9505,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9524,10 +9519,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45968</v>
+        <v>46200</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9540,7 +9535,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9583,7 +9578,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9597,10 +9592,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45922</v>
+        <v>45645</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9613,7 +9608,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9656,7 +9651,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9670,10 +9665,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45973</v>
+        <v>45181</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9686,7 +9681,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9729,7 +9724,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9743,10 +9738,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45973</v>
+        <v>45229</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9759,7 +9754,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9802,7 +9797,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9816,10 +9811,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45987</v>
+        <v>46206</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9832,7 +9827,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9875,7 +9870,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9889,10 +9884,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45987</v>
+        <v>45642</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9905,7 +9900,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.9</v>
+        <v>11.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9948,7 +9943,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9962,10 +9957,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45986</v>
+        <v>45642</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9978,7 +9973,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10021,7 +10016,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10035,10 +10030,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45989</v>
+        <v>46258</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10051,7 +10046,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10094,7 +10089,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10108,10 +10103,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46002</v>
+        <v>45191</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10124,7 +10119,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>14.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10167,7 +10162,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10181,10 +10176,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46002</v>
+        <v>45208</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10197,7 +10192,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10240,7 +10235,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10254,10 +10249,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46002</v>
+        <v>44817</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10270,7 +10265,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10313,7 +10308,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10327,10 +10322,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46002</v>
+        <v>45279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10386,7 +10381,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10400,10 +10395,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46007</v>
+        <v>46272</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10416,7 +10411,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10459,7 +10454,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10473,10 +10468,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46006</v>
+        <v>45716</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10489,7 +10484,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10532,7 +10527,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10546,10 +10541,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46007</v>
+        <v>45716</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10562,7 +10557,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>10.2</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10605,7 +10600,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10619,10 +10614,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46007</v>
+        <v>46272</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10635,7 +10630,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10678,7 +10673,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10692,10 +10687,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46008</v>
+        <v>46269</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10708,7 +10703,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10751,7 +10746,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10765,10 +10760,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46008</v>
+        <v>44907</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10781,7 +10776,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10824,7 +10819,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10838,10 +10833,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46009</v>
+        <v>45261</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,7 +10849,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10897,7 +10892,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10906,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45639</v>
+        <v>45520</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10922,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>10.3</v>
+        <v>2.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10965,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10979,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46073</v>
+        <v>46275</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11000,7 +10995,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11043,7 +11038,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11053,14 +11048,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46126</v>
+        <v>44902</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11073,7 +11068,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11116,7 +11111,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11125,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45873</v>
+        <v>45597</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11141,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11184,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11198,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46009</v>
+        <v>45671</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11219,7 +11214,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11257,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11272,14 +11267,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46146</v>
+        <v>46286</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11292,7 +11287,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11330,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11349,10 +11344,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46146</v>
+        <v>45076</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11360,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11403,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11417,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46155</v>
+        <v>45103</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11433,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11476,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11490,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46154</v>
+        <v>45256</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11506,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11549,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 39269-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11563,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45974</v>
+        <v>46288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11579,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11622,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 39266-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11636,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45462</v>
+        <v>46288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11652,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>11.1</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11695,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11714,10 +11709,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46009</v>
+        <v>45642</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11725,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11768,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11787,10 +11782,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45974</v>
+        <v>45425</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11802,8 +11797,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2.6</v>
+        <v>13.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45974</v>
+        <v>46247</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>15.3</v>
+        <v>2.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46200</v>
+        <v>45553</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>11.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46206</v>
+        <v>45700</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46258</v>
+        <v>45405</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46272</v>
+        <v>45405</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46272</v>
+        <v>45229</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46269</v>
+        <v>45099</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12367,14 +12367,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46275</v>
+        <v>45610</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45671</v>
+        <v>46253</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 38860-2026</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12513,14 +12513,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46286</v>
+        <v>44928</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 39266-2026</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46288</v>
+        <v>45776</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 39269-2026</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46288</v>
+        <v>44889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46247</v>
+        <v>45789</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46253</v>
+        <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
         <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 1855-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44884</v>
+        <v>45671</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -647,12 +647,130 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Gammelgransskål
+Tretåig hackspett
+Ullticka
+Lappranunkel
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Z2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 41136-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
         <v>26</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>26</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -662,157 +780,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 1855-2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Gammelgransskål
-Tretåig hackspett
-Ullticka
-Lappranunkel
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44886</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44883</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44496</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45716</v>
+        <v>45359</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45173</v>
+        <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45173</v>
+        <v>45685</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45405</v>
+        <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44901</v>
+        <v>45261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45103</v>
+        <v>45716</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45796</v>
+        <v>46002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.9</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45894</v>
+        <v>46002</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45903</v>
+        <v>46002</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45903</v>
+        <v>45789</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44872</v>
+        <v>46007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45639</v>
+        <v>46006</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10.3</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45209</v>
+        <v>45076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45579</v>
+        <v>46007</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45910</v>
+        <v>45645</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45636</v>
+        <v>46007</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45590</v>
+        <v>46008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45922</v>
+        <v>46008</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45922</v>
+        <v>46009</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45922</v>
+        <v>45894</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46073</v>
+        <v>45903</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45936</v>
+        <v>45636</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>18.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45068</v>
+        <v>45636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.6</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45943</v>
+        <v>45597</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45945</v>
+        <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.7</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45946</v>
+        <v>45910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45946</v>
+        <v>45796</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>10.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45581</v>
+        <v>45209</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45359</v>
+        <v>44629</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>13.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45953</v>
+        <v>45579</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45953</v>
+        <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45180</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45968</v>
+        <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45966</v>
+        <v>45639</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>10.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45973</v>
+        <v>45936</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45973</v>
+        <v>45581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5057,14 +5057,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46126</v>
+        <v>46073</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45581</v>
+        <v>45943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45986</v>
+        <v>45597</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44482</v>
+        <v>45945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.4</v>
+        <v>7.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45645</v>
+        <v>45946</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45987</v>
+        <v>45068</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45987</v>
+        <v>45946</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5558,7 +5558,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45989</v>
+        <v>45953</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46009</v>
+        <v>44872</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5704,7 +5704,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44750</v>
+        <v>45953</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5733,13 +5733,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5782,7 +5777,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5796,10 +5791,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45824</v>
+        <v>45597</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5807,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>17.8</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5850,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46002</v>
+        <v>45369</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5880,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>12.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5923,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5942,10 +5937,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46002</v>
+        <v>45966</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5953,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +5996,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45873</v>
+        <v>45968</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6026,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6069,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6088,10 +6083,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46002</v>
+        <v>45973</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6147,7 +6142,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6161,10 +6156,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46002</v>
+        <v>45973</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6177,7 +6172,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6220,7 +6215,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6234,10 +6229,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46006</v>
+        <v>45520</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6250,7 +6245,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,7 +6288,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6307,10 +6302,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46007</v>
+        <v>45103</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6323,7 +6318,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6366,7 +6361,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6380,10 +6375,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46007</v>
+        <v>45645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6396,7 +6391,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6439,7 +6434,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6453,10 +6448,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46007</v>
+        <v>45987</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6469,7 +6464,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>10.2</v>
+        <v>3.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6512,7 +6507,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6526,10 +6521,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46008</v>
+        <v>45044</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6542,7 +6537,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6585,7 +6580,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6599,10 +6594,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46008</v>
+        <v>45987</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6615,7 +6610,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>4.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6658,7 +6653,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6672,10 +6667,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45835</v>
+        <v>45197</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6688,7 +6683,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6731,7 +6726,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6745,10 +6740,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45217</v>
+        <v>45986</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6761,7 +6756,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6804,7 +6799,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6818,10 +6813,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45685</v>
+        <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6834,7 +6829,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6877,7 +6872,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6891,10 +6886,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45685</v>
+        <v>45824</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6907,7 +6902,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6950,7 +6945,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6960,14 +6955,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45197</v>
+        <v>46126</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6980,7 +6975,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7023,7 +7018,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7037,10 +7032,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44629</v>
+        <v>45716</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7053,7 +7048,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>13.3</v>
+        <v>3.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7096,7 +7091,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7106,14 +7101,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45044</v>
+        <v>45142</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7126,7 +7121,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7169,7 +7164,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7183,10 +7178,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44813</v>
+        <v>45581</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7199,7 +7194,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7242,7 +7237,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7252,14 +7247,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46146</v>
+        <v>45610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7272,7 +7267,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7315,7 +7310,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7329,10 +7324,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46146</v>
+        <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7345,7 +7340,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7388,7 +7383,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7402,10 +7397,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45597</v>
+        <v>45636</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7418,7 +7413,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7461,7 +7456,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7475,10 +7470,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45278</v>
+        <v>45078</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7491,7 +7486,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7534,7 +7529,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7548,10 +7543,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46154</v>
+        <v>45229</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7564,7 +7559,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7607,7 +7602,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7617,14 +7612,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45303</v>
+        <v>45425</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7636,8 +7631,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>13.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45369</v>
+        <v>45181</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>12.4</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45974</v>
+        <v>45873</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46155</v>
+        <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44949</v>
+        <v>45279</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44508</v>
+        <v>45405</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8055,14 +8055,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45142</v>
+        <v>45405</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45671</v>
+        <v>45642</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45974</v>
+        <v>44957</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46009</v>
+        <v>46146</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45462</v>
+        <v>46146</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>11.1</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45603</v>
+        <v>45208</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8493,14 +8493,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>44908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>15.3</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8566,14 +8566,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44908</v>
+        <v>45716</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44957</v>
+        <v>45716</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45597</v>
+        <v>44813</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45415</v>
+        <v>46155</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8848,7 +8848,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45129</v>
+        <v>46154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8921,7 +8921,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45355</v>
+        <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>27.1</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45636</v>
+        <v>45642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>18.6</v>
+        <v>11.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9067,7 +9067,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9081,10 +9081,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44579</v>
+        <v>45642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9140,7 +9140,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45636</v>
+        <v>44750</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9169,8 +9169,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9213,7 +9218,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9227,10 +9232,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45103</v>
+        <v>45462</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9243,7 +9248,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>11.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9286,7 +9291,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9300,10 +9305,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45078</v>
+        <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9316,7 +9321,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9359,7 +9364,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9373,10 +9378,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44586</v>
+        <v>45974</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9389,7 +9394,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9432,7 +9437,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9446,10 +9451,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45716</v>
+        <v>45974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9462,7 +9467,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>15.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9505,7 +9510,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 29093-2026</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9519,10 +9524,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46200</v>
+        <v>45603</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9535,7 +9540,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9578,7 +9583,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9592,10 +9597,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45645</v>
+        <v>45278</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9608,7 +9613,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9651,7 +9656,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9665,10 +9670,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45181</v>
+        <v>44508</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9681,7 +9686,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9724,7 +9729,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9738,10 +9743,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45229</v>
+        <v>44482</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9754,7 +9759,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9797,7 +9802,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9811,10 +9816,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46206</v>
+        <v>45671</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9827,7 +9832,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9870,7 +9875,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 29093-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9884,10 +9889,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45642</v>
+        <v>46200</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9900,7 +9905,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>11.7</v>
+        <v>2.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9943,7 +9948,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9957,10 +9962,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45642</v>
+        <v>44817</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9973,7 +9978,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10016,7 +10021,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10030,10 +10035,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46258</v>
+        <v>45256</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10046,7 +10051,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10089,7 +10094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10103,10 +10108,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45191</v>
+        <v>46206</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10119,7 +10124,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>14.9</v>
+        <v>2.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10162,7 +10167,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10176,10 +10181,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45208</v>
+        <v>45173</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10192,7 +10197,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10235,7 +10240,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10249,10 +10254,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44817</v>
+        <v>45173</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10265,7 +10270,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10308,7 +10313,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10322,10 +10327,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45279</v>
+        <v>46258</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10338,7 +10343,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10381,7 +10386,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10395,10 +10400,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46272</v>
+        <v>45405</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10454,7 +10459,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10468,10 +10473,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45716</v>
+        <v>44901</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10484,7 +10489,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>12.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10527,7 +10532,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10541,10 +10546,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45716</v>
+        <v>45415</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10557,7 +10562,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10600,7 +10605,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36682-2026</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10614,10 +10619,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46272</v>
+        <v>45191</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10630,7 +10635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.6</v>
+        <v>14.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10673,7 +10678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 36743-2026</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10687,10 +10692,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10703,7 +10708,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10746,7 +10751,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 36682-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10760,10 +10765,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44907</v>
+        <v>46272</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10776,7 +10781,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10819,7 +10824,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 36743-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10833,10 +10838,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45261</v>
+        <v>46269</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10849,7 +10854,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10892,7 +10897,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10906,10 +10911,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45520</v>
+        <v>45217</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10922,7 +10927,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10965,7 +10970,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 37395-2026</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10979,10 +10984,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46275</v>
+        <v>45129</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -10995,7 +11000,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11038,7 +11043,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 37395-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11052,10 +11057,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44902</v>
+        <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11068,7 +11073,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11111,7 +11116,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11125,10 +11130,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45597</v>
+        <v>45590</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11141,7 +11146,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11184,7 +11189,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11198,10 +11203,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45671</v>
+        <v>44586</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11214,7 +11219,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>7.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11257,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 38860-2026</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11267,14 +11272,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46286</v>
+        <v>45671</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11287,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11330,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11340,14 +11345,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45076</v>
+        <v>46286</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11360,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>10.5</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11403,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11417,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45103</v>
+        <v>44949</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11433,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11476,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11490,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45256</v>
+        <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11506,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11549,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 39269-2026</t>
+          <t>A 39266-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11566,7 +11571,7 @@
         <v>46288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11579,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11622,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 39266-2026</t>
+          <t>A 39269-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11639,7 +11644,7 @@
         <v>46288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11652,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11695,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11709,10 +11714,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11725,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11768,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11778,14 +11783,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45425</v>
+        <v>45303</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11797,13 +11802,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>13.9</v>
+        <v>1.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11863,7 +11863,7 @@
         <v>46247</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45553</v>
+        <v>45180</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>11.7</v>
+        <v>2.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45700</v>
+        <v>45355</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.4</v>
+        <v>27.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45405</v>
+        <v>46253</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45405</v>
+        <v>45103</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45229</v>
+        <v>45700</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45099</v>
+        <v>45685</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.6</v>
+        <v>11.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12367,14 +12367,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45610</v>
+        <v>44902</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46253</v>
+        <v>45553</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>6.4</v>
+        <v>11.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44928</v>
+        <v>44907</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45776</v>
+        <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12666,7 +12666,7 @@
         <v>44889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45789</v>
+        <v>45776</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12812,7 +12812,7 @@
         <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45671</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45173</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44886</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44883</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44496</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45359</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45685</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>45261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45716</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>46002</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>46002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>46002</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46002</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>45789</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>46007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>46006</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46007</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>45645</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>46007</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>46008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>46008</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>46009</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>45894</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45903</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>45636</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45597</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45796</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45209</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44629</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45579</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45639</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45936</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>46073</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>45597</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45946</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>45068</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45946</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45953</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44872</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45953</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45597</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45369</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45966</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45968</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>45973</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45973</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>45520</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45103</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45987</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45044</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45987</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45197</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45986</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>45824</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>46126</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45716</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>45142</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45581</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>45610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45636</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>45078</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>45229</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45425</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45181</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45873</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45279</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45405</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>45405</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>45642</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44957</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>46146</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>46146</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45208</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45716</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45716</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44813</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>46155</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>46154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44750</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>45462</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45974</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45603</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45278</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44508</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44482</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45671</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>46200</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>44817</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45256</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>46206</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45173</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45173</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>46258</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45405</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44901</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45415</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>45191</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>46272</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>46272</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>46269</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45217</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>45129</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>45590</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44586</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>45671</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>46286</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44949</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>46288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>46288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>45229</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>45303</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>46247</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>45180</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>45355</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>46253</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45103</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45700</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45685</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44902</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45553</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44907</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45776</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45671</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45173</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44886</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44883</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44496</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45359</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45685</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>45261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45716</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>46002</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>46002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>46002</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46002</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>45789</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>46007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>46006</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46007</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>45645</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>46007</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>46008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>46008</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>46009</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>45894</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45903</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>45636</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45636</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45597</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45796</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45209</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44629</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45579</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45639</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45936</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>46073</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>45597</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45946</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>45068</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45946</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45953</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44872</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45953</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45597</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45369</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45966</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45968</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>45973</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45973</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>45520</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45103</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45987</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45044</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45987</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45197</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45986</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>45824</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>46126</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45716</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>45142</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45581</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>45610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45636</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>45078</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>45229</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45425</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45181</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45873</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45279</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45405</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>45405</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>45642</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44957</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>46146</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>46146</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45208</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45716</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45716</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44813</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>46155</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>46154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44750</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>45462</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45974</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45603</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45278</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44508</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44482</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45671</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>46200</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>44817</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45256</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>46206</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45173</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45173</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>46258</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45405</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44901</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45415</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>45191</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>46272</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>46272</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>46269</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45217</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>45129</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>45590</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44586</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>45671</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>46286</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44949</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>46288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>46288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>45229</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>45303</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>46247</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>45180</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>45355</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>46253</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45103</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45700</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45685</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44902</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45553</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44907</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45776</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>45789</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 1855-2025</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45671</v>
+        <v>44884</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -647,12 +647,122 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
+        <v>26</v>
+      </c>
+      <c r="U2" t="n">
+        <v>26</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gammelgransskål
+Vedskivlav
+Nästlav
+Vedticka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 1855-2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45671</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gammelgransskål
@@ -662,115 +772,115 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 41136-2023</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>45173</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E4" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>5.7</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S4" t="n">
         <v>6</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>26</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>26</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -780,145 +890,35 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 54858-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44884</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>26</v>
-      </c>
-      <c r="U4" t="n">
-        <v>26</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gammelgransskål
-Vedskivlav
-Nästlav
-Vedticka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 21714-2026</t>
+          <t>A 63800-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46149</v>
+        <v>45278</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1099,159 +1099,159 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 21714-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Rödvingetrast</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 63800-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45278</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Trana</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49284-2022</t>
+          <t>A 28542-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44861</v>
+        <v>44748</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28542-2022</t>
+          <t>A 49284-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44748</v>
+        <v>44861</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44886</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44883</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44496</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45359</v>
+        <v>45716</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2477-2022</t>
+          <t>A 41134-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44579</v>
+        <v>45173</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 41135-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45685</v>
+        <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30141-2023</t>
+          <t>A 16036-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45099</v>
+        <v>45405</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 61570-2023</t>
+          <t>A 58379-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45261</v>
+        <v>44901</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>9.199999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9745-2025</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45716</v>
+        <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46002</v>
+        <v>44872</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61609-2025</t>
+          <t>A 58953-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46002</v>
+        <v>45636</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61623-2025</t>
+          <t>A 48383-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46002</v>
+        <v>45590</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61626-2025</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46002</v>
+        <v>45068</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22703-2025</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45789</v>
+        <v>45824</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.7</v>
+        <v>17.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62387-2025</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46007</v>
+        <v>45894</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62326-2025</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46006</v>
+        <v>45835</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23484-2023</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45076</v>
+        <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62384-2025</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46007</v>
+        <v>45903</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 61075-2024</t>
+          <t>A 46296-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45645</v>
+        <v>45581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62543-2025</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46007</v>
+        <v>45359</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62785-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46008</v>
+        <v>45910</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62896-2025</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46008</v>
+        <v>45639</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>10.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63367-2025</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46009</v>
+        <v>45922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 43003-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45894</v>
+        <v>45180</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45903</v>
+        <v>45922</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 58950-2024</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45636</v>
+        <v>45922</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>18.6</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58981-2024</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45636</v>
+        <v>45581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 49907-2024</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45597</v>
+        <v>45936</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45903</v>
+        <v>45943</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 57254-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45910</v>
+        <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24120-2025</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45796</v>
+        <v>46073</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>10.9</v>
+        <v>4.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49007-2023</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45209</v>
+        <v>45645</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44629</v>
+        <v>45945</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>13.3</v>
+        <v>7.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45575-2024</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45579</v>
+        <v>45946</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45922</v>
+        <v>45946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 29159-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>44750</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4711,8 +4711,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4760,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,10 +4774,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45922</v>
+        <v>45953</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4785,7 +4790,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4833,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4842,10 +4847,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45639</v>
+        <v>45953</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4858,7 +4863,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10.3</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4901,7 +4906,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4915,10 +4920,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45936</v>
+        <v>45968</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4931,7 +4936,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4979,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46296-2024</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4988,10 +4993,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45581</v>
+        <v>45966</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5004,7 +5009,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5047,7 +5052,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5061,10 +5066,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46073</v>
+        <v>45973</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5077,7 +5082,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5120,7 +5125,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 52192-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5134,10 +5139,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45943</v>
+        <v>45217</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5150,7 +5155,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5193,7 +5198,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49902-2024</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5207,10 +5212,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45597</v>
+        <v>45973</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5223,7 +5228,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5266,7 +5271,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5280,10 +5285,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45945</v>
+        <v>45685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5296,7 +5301,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5339,7 +5344,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 4323-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5353,10 +5358,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45946</v>
+        <v>45685</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,7 +5374,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5412,7 +5417,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5426,10 +5431,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45068</v>
+        <v>45197</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5442,7 +5447,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5485,7 +5490,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5495,14 +5500,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45946</v>
+        <v>46126</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5515,7 +5520,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5558,7 +5563,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 58624-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5572,10 +5577,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45953</v>
+        <v>45986</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5588,7 +5593,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5631,7 +5636,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5645,10 +5650,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44872</v>
+        <v>44629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5661,7 +5666,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5</v>
+        <v>13.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5704,7 +5709,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 58943-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5718,10 +5723,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45953</v>
+        <v>45987</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5734,7 +5739,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5777,7 +5782,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49904-2024</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5791,10 +5796,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45597</v>
+        <v>45044</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5807,7 +5812,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5850,7 +5855,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 10735-2024</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5864,10 +5869,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45369</v>
+        <v>45987</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5880,7 +5885,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>12.4</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5923,7 +5928,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 59478-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5937,10 +5942,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45966</v>
+        <v>45989</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5953,7 +5958,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5996,7 +6001,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 61607-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45968</v>
+        <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6026,7 +6031,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6069,7 +6074,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 61626-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6083,10 +6088,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45973</v>
+        <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6099,7 +6104,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6142,7 +6147,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 38510-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6156,10 +6161,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45973</v>
+        <v>44813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6172,7 +6177,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6215,7 +6220,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33728-2024</t>
+          <t>A 61609-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6229,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45520</v>
+        <v>46002</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6245,7 +6250,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6288,7 +6293,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 61623-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6302,10 +6307,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45103</v>
+        <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6318,7 +6323,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6361,7 +6366,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 62326-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6375,10 +6380,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45645</v>
+        <v>46006</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6391,7 +6396,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6434,7 +6439,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6448,10 +6453,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45987</v>
+        <v>45597</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6464,7 +6469,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6507,7 +6512,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 62387-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6521,10 +6526,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45044</v>
+        <v>46007</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6537,7 +6542,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6580,7 +6585,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 62543-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6594,10 +6599,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45987</v>
+        <v>46007</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6610,7 +6615,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 62384-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45197</v>
+        <v>46007</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6683,7 +6688,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 62785-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6740,10 +6745,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45986</v>
+        <v>46008</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6756,7 +6761,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6799,7 +6804,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 62896-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6813,10 +6818,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45989</v>
+        <v>46008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6829,7 +6834,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6872,7 +6877,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 63850-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6886,10 +6891,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45824</v>
+        <v>45278</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6902,7 +6907,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>17.8</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6945,7 +6950,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 63367-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6955,14 +6960,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46126</v>
+        <v>46009</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6975,7 +6980,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7018,7 +7023,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 63369-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7032,10 +7037,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45716</v>
+        <v>46009</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7048,7 +7053,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>8.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7091,7 +7096,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34980-2023</t>
+          <t>A 1446-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7105,10 +7110,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45142</v>
+        <v>45303</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7121,7 +7126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7164,7 +7169,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7178,10 +7183,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45581</v>
+        <v>45369</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7194,7 +7199,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>12.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7237,7 +7242,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52735-2024</t>
+          <t>A 3498-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7247,14 +7252,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45610</v>
+        <v>44949</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7267,7 +7272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7310,7 +7315,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 63219-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7324,10 +7329,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45835</v>
+        <v>44508</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7340,7 +7345,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7383,7 +7388,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7393,14 +7398,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45636</v>
+        <v>45142</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7413,7 +7418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7456,7 +7461,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23982-2023</t>
+          <t>A 1870-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7470,10 +7475,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45078</v>
+        <v>45671</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7486,7 +7491,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7529,7 +7534,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53257-2023</t>
+          <t>A 36766-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7543,10 +7548,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45229</v>
+        <v>45873</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7559,7 +7564,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7602,7 +7607,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18652-2024</t>
+          <t>A 51376-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7616,10 +7621,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45425</v>
+        <v>45603</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7631,13 +7636,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>13.9</v>
+        <v>2.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42547-2023</t>
+          <t>A 61161-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7690,14 +7690,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45181</v>
+        <v>44908</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 36766-2025</t>
+          <t>A 5498-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45873</v>
+        <v>44957</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 63369-2025</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46009</v>
+        <v>45597</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 64139-2023</t>
+          <t>A 17564-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45279</v>
+        <v>45415</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16030-2024</t>
+          <t>A 21179-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45405</v>
+        <v>46146</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16035-2024</t>
+          <t>A 21205-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45405</v>
+        <v>46146</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 60217-2024</t>
+          <t>A 33439-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45642</v>
+        <v>45129</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 5498-2023</t>
+          <t>A 8836-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44957</v>
+        <v>45355</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>27.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21205-2026</t>
+          <t>A 22352-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21179-2026</t>
+          <t>A 56366-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46146</v>
+        <v>45974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8410,7 +8410,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48630-2023</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45208</v>
+        <v>45636</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.3</v>
+        <v>18.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61161-2022</t>
+          <t>A 22512-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8493,14 +8493,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44908</v>
+        <v>46155</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8556,7 +8556,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9738-2025</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45716</v>
+        <v>44579</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8629,7 +8629,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9739-2025</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45716</v>
+        <v>45636</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8702,7 +8702,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38510-2022</t>
+          <t>A 31242-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44813</v>
+        <v>45103</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 22512-2026</t>
+          <t>A 23982-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46155</v>
+        <v>45078</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8848,7 +8848,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 22352-2026</t>
+          <t>A 56356-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46154</v>
+        <v>45974</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8921,7 +8921,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56366-2025</t>
+          <t>A 63368-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45974</v>
+        <v>46009</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60214-2024</t>
+          <t>A 25164-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45642</v>
+        <v>45462</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9067,7 +9067,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60219-2024</t>
+          <t>A 56374-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9081,10 +9081,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45642</v>
+        <v>45974</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>15.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9140,7 +9140,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 3631-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44750</v>
+        <v>44586</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9169,13 +9169,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9218,7 +9213,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 25164-2024</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9232,10 +9227,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45462</v>
+        <v>45716</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9248,7 +9243,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>11.1</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9291,7 +9286,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 63368-2025</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9305,10 +9300,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46009</v>
+        <v>45645</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9321,7 +9316,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9364,7 +9359,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56356-2025</t>
+          <t>A 42547-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9378,10 +9373,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45974</v>
+        <v>45181</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9394,7 +9389,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9437,7 +9432,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 56374-2025</t>
+          <t>A 53257-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9451,10 +9446,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45974</v>
+        <v>45229</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9467,7 +9462,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>15.3</v>
+        <v>5.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9510,7 +9505,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 51376-2024</t>
+          <t>A 60214-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9524,10 +9519,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45603</v>
+        <v>45642</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9540,7 +9535,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.8</v>
+        <v>11.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9583,7 +9578,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 63850-2023</t>
+          <t>A 60219-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9597,10 +9592,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45278</v>
+        <v>45642</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9613,7 +9608,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9656,7 +9651,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 63219-2021</t>
+          <t>A 46305-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9670,10 +9665,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44508</v>
+        <v>45191</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9686,7 +9681,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>14.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9729,7 +9724,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 48630-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9743,10 +9738,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44482</v>
+        <v>45208</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9759,7 +9754,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9802,7 +9797,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1870-2025</t>
+          <t>A 41009-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9816,10 +9811,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45671</v>
+        <v>44817</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9832,7 +9827,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9892,7 +9887,7 @@
         <v>46200</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9948,7 +9943,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 41009-2022</t>
+          <t>A 64139-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9962,10 +9957,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44817</v>
+        <v>45279</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9978,7 +9973,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10021,7 +10016,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 59686-2023</t>
+          <t>A 9738-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10035,10 +10030,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45256</v>
+        <v>45716</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10051,7 +10046,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10094,7 +10089,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 30289-2026</t>
+          <t>A 9739-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10108,10 +10103,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46206</v>
+        <v>45716</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10124,7 +10119,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10167,7 +10162,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 30289-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10181,10 +10176,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45173</v>
+        <v>46206</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10197,7 +10192,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10240,7 +10235,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 60928-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10254,10 +10249,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45173</v>
+        <v>44907</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10313,7 +10308,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 34719-2026</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10327,10 +10322,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46258</v>
+        <v>45261</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10386,7 +10381,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10400,10 +10395,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45405</v>
+        <v>45520</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10416,7 +10411,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10459,7 +10454,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 60064-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10473,10 +10468,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44901</v>
+        <v>44902</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10489,7 +10484,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>12.1</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10532,7 +10527,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 17564-2024</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10546,10 +10541,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45415</v>
+        <v>45597</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10562,7 +10557,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10605,7 +10600,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 46305-2023</t>
+          <t>A 36680-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10619,10 +10614,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45191</v>
+        <v>46272</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10635,7 +10630,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>14.9</v>
+        <v>1.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10678,7 +10673,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 36680-2026</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10692,10 +10687,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46272</v>
+        <v>45076</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10708,7 +10703,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10768,7 +10763,7 @@
         <v>46272</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10841,7 +10836,7 @@
         <v>46269</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10897,7 +10892,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 31236-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10911,10 +10906,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45217</v>
+        <v>45103</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10927,7 +10922,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10970,7 +10965,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33439-2023</t>
+          <t>A 59686-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10984,10 +10979,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45129</v>
+        <v>45256</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11000,7 +10995,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11060,7 +11055,7 @@
         <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11116,7 +11111,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 60217-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11130,10 +11125,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45590</v>
+        <v>45642</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11146,7 +11141,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11189,7 +11184,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3631-2022</t>
+          <t>A 18652-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11203,10 +11198,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44586</v>
+        <v>45425</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11218,8 +11213,13 @@
           <t>HAPARANDA</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>7.9</v>
+        <v>13.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11262,7 +11262,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1849-2025</t>
+          <t>A 39893-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45671</v>
+        <v>45553</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>11.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 38860-2026</t>
+          <t>A 6806-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11345,14 +11345,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46286</v>
+        <v>45700</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11408,7 +11408,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 3498-2023</t>
+          <t>A 16030-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44949</v>
+        <v>45405</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31236-2023</t>
+          <t>A 16035-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45103</v>
+        <v>45405</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11554,7 +11554,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 39266-2026</t>
+          <t>A 1849-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46288</v>
+        <v>45671</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 39269-2026</t>
+          <t>A 53290-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46288</v>
+        <v>45229</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 53290-2023</t>
+          <t>A 38860-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11710,14 +11710,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45229</v>
+        <v>46286</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11773,7 +11773,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1446-2024</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11783,14 +11783,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45303</v>
+        <v>45099</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11846,7 +11846,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33404-2026</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11856,14 +11856,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46247</v>
+        <v>45610</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 277-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45180</v>
+        <v>44928</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11992,7 +11992,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8836-2024</t>
+          <t>A 39269-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45355</v>
+        <v>46288</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>27.1</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34283-2026</t>
+          <t>A 39266-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46253</v>
+        <v>46288</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 31242-2023</t>
+          <t>A 33404-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45103</v>
+        <v>46247</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6806-2025</t>
+          <t>A 20727-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45700</v>
+        <v>45776</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 56024-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45685</v>
+        <v>44889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60064-2022</t>
+          <t>A 34283-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44902</v>
+        <v>46253</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39893-2024</t>
+          <t>A 34719-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45553</v>
+        <v>46258</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>11.7</v>
+        <v>3.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12503,7 +12503,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 60928-2022</t>
+          <t>A 22703-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44907</v>
+        <v>45789</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 277-2023</t>
+          <t>A 22697-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44928</v>
+        <v>45789</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 56024-2022</t>
+          <t>A 24120-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44889</v>
+        <v>45796</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.3</v>
+        <v>10.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 20727-2025</t>
+          <t>A 49007-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45776</v>
+        <v>45209</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22697-2025</t>
+          <t>A 45575-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45789</v>
+        <v>45579</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
         <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>

--- a/Översikt HAPARANDA.xlsx
+++ b/Översikt HAPARANDA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54858-2022</t>
+          <t>A 1855-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44884</v>
+        <v>45671</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -647,12 +647,130 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Gammelgransskål
+Tretåig hackspett
+Ullticka
+Lappranunkel
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="Z2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 41136-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
         <v>26</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>26</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -662,157 +780,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 1855-2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Gammelgransskål
-Tretåig hackspett
-Ullticka
-Lappranunkel
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 1855-2025 artfynd.xlsx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 1855-2025 karta.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 1855-2025 georefererad karta.tif", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/knärot/A 1855-2025 karta knärot.png", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 1855-2025 FSC-klagomål.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 1855-2025 FSC-klagomål mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 1855-2025 tillsynsbegäran.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 1855-2025 tillsynsbegäran mail.docx", "A 1855-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 1855-2025 prioriterade fågelarter.docx", "A 1855-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 41136-2023</t>
+          <t>A 54858-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45173</v>
+        <v>44884</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 41136-2023 artfynd.xlsx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 54858-2022 artfynd.xlsx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 41136-2023 karta.png", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 54858-2022 karta.png", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 41136-2023 georefererad karta.tif", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 54858-2022 georefererad karta.tif", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 41136-2023 FSC-klagomål.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 54858-2022 FSC-klagomål.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 41136-2023 FSC-klagomål mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 54858-2022 FSC-klagomål mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 41136-2023 tillsynsbegäran.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 54858-2022 tillsynsbegäran.docx", "A 54858-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 41136-2023 tillsynsbegäran mail.docx", "A 41136-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 54858-2022 tillsynsbegäran mail.docx", "A 54858-2022")</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 63800-2023</t>
+          <t>A 21714-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45278</v>
+        <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1099,159 +1099,159 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 63800-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAPARANDA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Trana</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 63800-2023 artfynd.xlsx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 63800-2023 karta.png", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 63800-2023 georefererad karta.tif", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 63800-2023 FSC-klagomål.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 63800-2023 FSC-klagomål mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 63800-2023 tillsynsbegäran.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 63800-2023 tillsynsbegäran mail.docx", "A 63800-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 63800-2023 prioriterade fågelarter.docx", "A 63800-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 21714-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAPARANDA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/artfynd/A 21714-2026 artfynd.xlsx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor/A 21714-2026 karta.png", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/kartor_geotiff/A 21714-2026 georefererad karta.tif", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomål/A 21714-2026 FSC-klagomål.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/klagomålsmail/A 21714-2026 FSC-klagomål mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsyn/A 21714-2026 tillsynsbegäran.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/tillsynsmail/A 21714-2026 tillsynsbegäran mail.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2583/fåglar/A 21714-2026 prioriterade fågelarter.docx", "A 21714-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28542-2022</t>
+          <t>A 49284-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44748</v>
+        <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49284-2022</t>
+          <t>A 28542-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44861</v>
+        <v>44748</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>44883</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44509</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44571</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44509</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44861</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44756</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44886</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44883</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44496</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9748-2025</t>
+          <t>A 9488-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45716</v>
+        <v>45359</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41134-2023</t>
+          <t>A 2477-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45173</v>
+        <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41135-2023</t>
+          <t>A 4317-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45173</v>
+        <v>45685</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16036-2024</t>
+          <t>A 30141-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45405</v>
+        <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58379-2022</t>
+          <t>A 9745-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44901</v>
+        <v>45716</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12.1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31238-2023</t>
+          <t>A 61570-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45103</v>
+        <v>45261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52006-2022</t>
+          <t>A 23484-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44872</v>
+        <v>45076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58953-2024</t>
+          <t>A 61075-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45636</v>
+        <v>45645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 48383-2024</t>
+          <t>A 58950-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45590</v>
+        <v>45636</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.5</v>
+        <v>18.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21979-2023</t>
+          <t>A 58981-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45068</v>
+        <v>45636</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.6</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29319-2025</t>
+          <t>A 49907-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45824</v>
+        <v>45597</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>17.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40100-2025</t>
+          <t>A 11285-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45894</v>
+        <v>44629</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>13.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32033-2025</t>
+          <t>A 21979-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45835</v>
+        <v>45068</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>8.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41946-2025</t>
+          <t>A 40100-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45903</v>
+        <v>45894</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 41945-2025</t>
+          <t>A 59847-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45903</v>
+        <v>45639</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>10.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>45581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9488-2024</t>
+          <t>A 49902-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45359</v>
+        <v>45597</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43215-2025</t>
+          <t>A 41945-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59847-2024</t>
+          <t>A 41946-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45639</v>
+        <v>45903</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10.3</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45356-2025</t>
+          <t>A 43215-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45922</v>
+        <v>45910</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43003-2023</t>
+          <t>A 52006-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45180</v>
+        <v>44872</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45362-2025</t>
+          <t>A 49904-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45922</v>
+        <v>45597</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45358-2025</t>
+          <t>A 10074-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45922</v>
+        <v>46073</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46301-2024</t>
+          <t>A 29319-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45581</v>
+        <v>45824</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>17.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 48599-2025</t>
+          <t>A 45358-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45936</v>
+        <v>45922</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 50085-2025</t>
+          <t>A 45362-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45943</v>
+        <v>45922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57254-2021</t>
+          <t>A 45356-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44482</v>
+        <v>45922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10074-2026</t>
+          <t>A 10735-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46073</v>
+        <v>45369</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.1</v>
+        <v>12.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61068-2024</t>
+          <t>A 32033-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45645</v>
+        <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 50450-2025</t>
+          <t>A 48599-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45945</v>
+        <v>45936</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50785-2025</t>
+          <t>A 33728-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45946</v>
+        <v>45520</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4609,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 50793-2025</t>
+          <t>A 50085-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45946</v>
+        <v>45943</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29159-2022</t>
+          <t>A 50450-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44750</v>
+        <v>45945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4711,13 +4711,8 @@
           <t>HAPARANDA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>7.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4760,7 +4755,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52322-2025</t>
+          <t>A 31238-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4774,10 +4769,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45953</v>
+        <v>45103</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4790,7 +4785,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4833,7 +4828,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52331-2025</t>
+          <t>A 61068-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4847,10 +4842,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45953</v>
+        <v>45645</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4863,7 +4858,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4906,7 +4901,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55192-2025</t>
+          <t>A 50785-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4920,10 +4915,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45968</v>
+        <v>45946</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4936,7 +4931,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4979,7 +4974,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54856-2025</t>
+          <t>A 50793-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4993,10 +4988,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45966</v>
+        <v>45946</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5009,7 +5004,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5052,7 +5047,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55861-2025</t>
+          <t>A 18855-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5066,10 +5061,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45973</v>
+        <v>45044</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5082,7 +5077,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5125,7 +5120,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52192-2023</t>
+          <t>A 46301-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5139,10 +5134,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45217</v>
+        <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5155,7 +5150,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5198,7 +5193,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55875-2025</t>
+          <t>A 52331-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5212,10 +5207,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45973</v>
+        <v>45953</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5228,7 +5223,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5271,7 +5266,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4317-2025</t>
+          <t>A 52322-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5285,10 +5280,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45685</v>
+        <v>45953</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5301,7 +5296,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5344,7 +5339,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4323-2025</t>
+          <t>A 18413-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5354,14 +5349,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45685</v>
+        <v>46126</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5374,7 +5369,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>11.1</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5417,7 +5412,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46301-2023</t>
+          <t>A 9748-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5431,10 +5426,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45197</v>
+        <v>45716</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5447,7 +5442,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5490,7 +5485,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18413-2026</t>
+          <t>A 54856-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5500,14 +5495,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46126</v>
+        <v>45966</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5520,7 +5515,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5563,7 +5558,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58624-2025</t>
+          <t>A 55192-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5577,10 +5572,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45986</v>
+        <v>45968</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5593,7 +5588,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5636,7 +5631,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11285-2022</t>
+          <t>A 55861-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5650,10 +5645,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44629</v>
+        <v>45973</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5666,7 +5661,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>13.3</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5709,7 +5704,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58943-2025</t>
+          <t>A 55875-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5723,10 +5718,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45987</v>
+        <v>45973</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5782,7 +5777,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18855-2023</t>
+          <t>A 34980-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5792,14 +5787,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45044</v>
+        <v>45142</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5812,7 +5807,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5855,7 +5850,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58851-2025</t>
+          <t>A 46301-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45987</v>
+        <v>45581</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5885,7 +5880,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5928,7 +5923,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59478-2025</t>
+          <t>A 52735-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5938,14 +5933,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45989</v>
+        <v>45610</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5958,7 +5953,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6001,7 +5996,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61607-2025</t>
+          <t>A 58851-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46002</v>
+        <v>45987</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6031,7 +6026,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6074,7 +6069,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-       